--- a/00 Reference Document/config/LAR_AEL metadata.xlsx
+++ b/00 Reference Document/config/LAR_AEL metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Test_Code\TOV_Final\CheckerProgram_Manoj\metadataV5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Smart Maintanence\TOV1050_Analyzer\00 Reference Document\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2735A4A0-196A-4B8D-AB7B-8240D14B85E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A5CA40-BDDB-486C-A287-32075E08F54D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="180" windowWidth="14355" windowHeight="15210" xr2:uid="{40971268-6843-45A4-929F-390CE8EC23ED}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{40971268-6843-45A4-929F-390CE8EC23ED}"/>
   </bookViews>
   <sheets>
     <sheet name="threshold" sheetId="3" r:id="rId1"/>
@@ -301,9 +301,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -341,7 +341,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -447,7 +447,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -589,7 +589,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -598,16 +598,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA354EF1-BC8A-4D36-9E77-3C91C8F99CA2}">
   <dimension ref="A1:F89"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" customWidth="1"/>
-    <col min="6" max="6" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" customWidth="1"/>
+    <col min="3" max="3" width="15.81640625" customWidth="1"/>
+    <col min="5" max="5" width="9.1796875" customWidth="1"/>
+    <col min="6" max="6" width="39.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -627,7 +627,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>28</v>
       </c>
@@ -645,7 +645,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="11" t="s">
         <v>28</v>
       </c>
@@ -665,7 +665,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
         <v>28</v>
       </c>
@@ -685,7 +685,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
         <v>28</v>
       </c>
@@ -703,7 +703,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
         <v>28</v>
       </c>
@@ -721,7 +721,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
         <v>28</v>
       </c>
@@ -741,7 +741,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>28</v>
       </c>
@@ -761,7 +761,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
         <v>28</v>
       </c>
@@ -779,7 +779,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
         <v>28</v>
       </c>
@@ -797,7 +797,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>28</v>
       </c>
@@ -817,7 +817,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
         <v>28</v>
       </c>
@@ -835,7 +835,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
         <v>28</v>
       </c>
@@ -855,7 +855,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
         <v>28</v>
       </c>
@@ -875,7 +875,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
         <v>28</v>
       </c>
@@ -893,7 +893,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
         <v>28</v>
       </c>
@@ -913,7 +913,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
         <v>28</v>
       </c>
@@ -931,7 +931,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="15" t="s">
         <v>35</v>
       </c>
@@ -951,7 +951,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="15" t="s">
         <v>35</v>
       </c>
@@ -969,7 +969,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="15" t="s">
         <v>35</v>
       </c>
@@ -989,7 +989,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="15" t="s">
         <v>35</v>
       </c>
@@ -1007,7 +1007,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="15" t="s">
         <v>34</v>
       </c>
@@ -1027,7 +1027,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" s="15" t="s">
         <v>34</v>
       </c>
@@ -1045,7 +1045,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A24" s="15" t="s">
         <v>34</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A25" s="15" t="s">
         <v>34</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="15" t="s">
         <v>35</v>
       </c>
@@ -1101,7 +1101,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="15" t="s">
         <v>35</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="15" t="s">
         <v>35</v>
       </c>
@@ -1141,7 +1141,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="15" t="s">
         <v>35</v>
       </c>
@@ -1159,7 +1159,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="15" t="s">
         <v>35</v>
       </c>
@@ -1177,7 +1177,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="15" t="s">
         <v>35</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="15" t="s">
         <v>35</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="15" t="s">
         <v>35</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="15" t="s">
         <v>34</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="15" t="s">
         <v>34</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="15" t="s">
         <v>34</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="15" t="s">
         <v>34</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="15" t="s">
         <v>34</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="15" t="s">
         <v>34</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="15" t="s">
         <v>34</v>
       </c>
@@ -1369,7 +1369,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="15" t="s">
         <v>34</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>12</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>12</v>
       </c>
@@ -1497,7 +1497,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>12</v>
       </c>
@@ -1517,7 +1517,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>12</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>12</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>12</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>12</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>12</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>6</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>6</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>6</v>
       </c>
@@ -1682,7 +1682,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>6</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>6</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>6</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>12</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>12</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>12</v>
       </c>
@@ -1810,7 +1810,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>12</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>6</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>6</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>12</v>
       </c>
@@ -1881,7 +1881,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>12</v>
       </c>
@@ -1898,7 +1898,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>6</v>
       </c>
@@ -1915,7 +1915,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>6</v>
       </c>
@@ -1935,7 +1935,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>6</v>
       </c>
@@ -1955,7 +1955,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>6</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>6</v>
       </c>
@@ -1992,7 +1992,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>6</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>6</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>6</v>
       </c>
@@ -2049,7 +2049,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>6</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>6</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>12</v>
       </c>
@@ -2103,7 +2103,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>12</v>
       </c>
@@ -2123,7 +2123,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>12</v>
       </c>
@@ -2143,7 +2143,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>12</v>
       </c>
@@ -2163,7 +2163,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>12</v>
       </c>
@@ -2180,7 +2180,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>12</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>12</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>12</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>12</v>
       </c>
@@ -2257,7 +2257,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>12</v>
       </c>
@@ -2284,15 +2284,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4B4D9E9-39BD-4101-B02D-2FB2C2CEDBBB}">
   <dimension ref="A1:D495"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" style="10" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" customWidth="1"/>
+    <col min="1" max="1" width="14.54296875" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" style="10" customWidth="1"/>
+    <col min="4" max="4" width="17.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>22</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>24.587900000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="D8" s="4"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="D10" s="4"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="D12" s="4"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="D14" s="4"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="D16" s="4"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="D18" s="4"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="D20" s="4"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="D22" s="4"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>13</v>
       </c>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="D24" s="4"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>7</v>
       </c>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="D26" s="4"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>13</v>
       </c>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="D27" s="4"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>7</v>
       </c>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="D28" s="4"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>13</v>
       </c>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="D29" s="4"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="D30" s="4"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>13</v>
       </c>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>7</v>
       </c>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="D32" s="4"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>13</v>
       </c>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>7</v>
       </c>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="D34" s="4"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>13</v>
       </c>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="D35" s="4"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>7</v>
       </c>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="D36" s="4"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>13</v>
       </c>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="D37" s="4"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>7</v>
       </c>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="D38" s="4"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>13</v>
       </c>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>7</v>
       </c>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="D40" s="4"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>13</v>
       </c>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="D41" s="4"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>7</v>
       </c>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="D42" s="4"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>13</v>
       </c>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="D43" s="4"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>7</v>
       </c>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="D44" s="4"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>13</v>
       </c>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>7</v>
       </c>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="D46" s="4"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>13</v>
       </c>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="D47" s="4"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>7</v>
       </c>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D48" s="4"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>13</v>
       </c>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="D49" s="4"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>7</v>
       </c>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="D50" s="4"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>13</v>
       </c>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="D51" s="4"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="D52" s="4"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>13</v>
       </c>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="D53" s="4"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>7</v>
       </c>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="D54" s="4"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>13</v>
       </c>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="D55" s="4"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>7</v>
       </c>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>13</v>
       </c>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="D57" s="4"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="D58" s="4"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>13</v>
       </c>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D59" s="4"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>7</v>
       </c>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="D60" s="4"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>13</v>
       </c>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="D61" s="4"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>7</v>
       </c>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="D62" s="4"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>13</v>
       </c>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D63" s="4"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>7</v>
       </c>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="D64" s="4"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>13</v>
       </c>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="D65" s="4"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>7</v>
       </c>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="D66" s="4"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>13</v>
       </c>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="D67" s="4"/>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>7</v>
       </c>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D68" s="4"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>13</v>
       </c>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="D69" s="4"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>7</v>
       </c>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="D70" s="4"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>13</v>
       </c>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="D71" s="4"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>7</v>
       </c>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="D72" s="4"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>13</v>
       </c>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="D73" s="4"/>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>7</v>
       </c>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="D74" s="4"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>13</v>
       </c>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="D75" s="4"/>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>7</v>
       </c>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="D76" s="4"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>13</v>
       </c>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="D77" s="4"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>7</v>
       </c>
@@ -3226,1691 +3226,1691 @@
       </c>
       <c r="D78" s="4"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B79" s="9"/>
       <c r="C79" s="9"/>
       <c r="D79" s="4"/>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D80" s="4"/>
     </row>
-    <row r="81" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B81" s="9"/>
       <c r="C81" s="9"/>
       <c r="D81" s="4"/>
     </row>
-    <row r="82" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D82" s="4"/>
     </row>
-    <row r="83" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B83" s="9"/>
       <c r="C83" s="9"/>
       <c r="D83" s="4"/>
     </row>
-    <row r="84" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D84" s="4"/>
     </row>
-    <row r="85" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B85" s="9"/>
       <c r="C85" s="9"/>
       <c r="D85" s="4"/>
     </row>
-    <row r="86" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D86" s="4"/>
     </row>
-    <row r="87" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B87" s="9"/>
       <c r="C87" s="9"/>
       <c r="D87" s="4"/>
     </row>
-    <row r="88" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D88" s="4"/>
     </row>
-    <row r="89" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B89" s="9"/>
       <c r="C89" s="9"/>
       <c r="D89" s="4"/>
     </row>
-    <row r="90" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D90" s="4"/>
     </row>
-    <row r="91" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B91" s="9"/>
       <c r="C91" s="9"/>
       <c r="D91" s="4"/>
     </row>
-    <row r="92" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D92" s="4"/>
     </row>
-    <row r="93" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B93" s="9"/>
       <c r="C93" s="9"/>
       <c r="D93" s="4"/>
     </row>
-    <row r="94" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D94" s="4"/>
     </row>
-    <row r="95" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B95" s="9"/>
       <c r="C95" s="9"/>
       <c r="D95" s="4"/>
     </row>
-    <row r="96" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D96" s="4"/>
     </row>
-    <row r="97" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B97" s="9"/>
       <c r="C97" s="9"/>
       <c r="D97" s="4"/>
     </row>
-    <row r="98" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D98" s="4"/>
     </row>
-    <row r="99" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B99" s="9"/>
       <c r="C99" s="9"/>
       <c r="D99" s="4"/>
     </row>
-    <row r="100" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D100" s="4"/>
     </row>
-    <row r="101" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B101" s="9"/>
       <c r="C101" s="9"/>
       <c r="D101" s="4"/>
     </row>
-    <row r="102" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D102" s="4"/>
     </row>
-    <row r="103" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B103" s="9"/>
       <c r="C103" s="9"/>
       <c r="D103" s="4"/>
     </row>
-    <row r="104" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D104" s="4"/>
     </row>
-    <row r="105" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B105" s="9"/>
       <c r="C105" s="9"/>
       <c r="D105" s="4"/>
     </row>
-    <row r="106" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D106" s="4"/>
     </row>
-    <row r="107" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B107" s="9"/>
       <c r="C107" s="9"/>
       <c r="D107" s="4"/>
     </row>
-    <row r="108" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D108" s="4"/>
     </row>
-    <row r="109" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B109" s="9"/>
       <c r="C109" s="9"/>
       <c r="D109" s="4"/>
     </row>
-    <row r="110" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D110" s="4"/>
     </row>
-    <row r="111" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B111" s="9"/>
       <c r="C111" s="9"/>
       <c r="D111" s="4"/>
     </row>
-    <row r="112" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D112" s="4"/>
     </row>
-    <row r="113" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B113" s="9"/>
       <c r="C113" s="9"/>
       <c r="D113" s="4"/>
     </row>
-    <row r="114" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D114" s="4"/>
     </row>
-    <row r="115" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B115" s="9"/>
       <c r="C115" s="9"/>
       <c r="D115" s="4"/>
     </row>
-    <row r="116" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D116" s="4"/>
     </row>
-    <row r="117" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B117" s="9"/>
       <c r="C117" s="9"/>
       <c r="D117" s="4"/>
     </row>
-    <row r="118" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D118" s="4"/>
     </row>
-    <row r="119" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B119" s="9"/>
       <c r="C119" s="9"/>
       <c r="D119" s="4"/>
     </row>
-    <row r="120" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D120" s="4"/>
     </row>
-    <row r="121" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B121" s="9"/>
       <c r="C121" s="9"/>
       <c r="D121" s="4"/>
     </row>
-    <row r="122" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D122" s="4"/>
     </row>
-    <row r="123" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B123" s="9"/>
       <c r="C123" s="9"/>
       <c r="D123" s="4"/>
     </row>
-    <row r="124" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D124" s="4"/>
     </row>
-    <row r="125" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B125" s="9"/>
       <c r="C125" s="9"/>
       <c r="D125" s="4"/>
     </row>
-    <row r="126" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D126" s="4"/>
     </row>
-    <row r="127" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B127" s="9"/>
       <c r="C127" s="9"/>
       <c r="D127" s="4"/>
     </row>
-    <row r="128" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D128" s="4"/>
     </row>
-    <row r="129" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B129" s="9"/>
       <c r="C129" s="9"/>
       <c r="D129" s="4"/>
     </row>
-    <row r="130" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D130" s="4"/>
     </row>
-    <row r="131" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B131" s="9"/>
       <c r="C131" s="9"/>
       <c r="D131" s="4"/>
     </row>
-    <row r="132" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D132" s="4"/>
     </row>
-    <row r="133" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B133" s="9"/>
       <c r="C133" s="9"/>
       <c r="D133" s="4"/>
     </row>
-    <row r="134" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D134" s="4"/>
     </row>
-    <row r="135" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B135" s="9"/>
       <c r="C135" s="9"/>
       <c r="D135" s="4"/>
     </row>
-    <row r="136" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D136" s="4"/>
     </row>
-    <row r="137" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B137" s="9"/>
       <c r="C137" s="9"/>
       <c r="D137" s="4"/>
     </row>
-    <row r="138" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D138" s="4"/>
     </row>
-    <row r="139" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B139" s="9"/>
       <c r="C139" s="9"/>
       <c r="D139" s="4"/>
     </row>
-    <row r="140" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D140" s="4"/>
     </row>
-    <row r="141" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B141" s="9"/>
       <c r="C141" s="9"/>
       <c r="D141" s="4"/>
     </row>
-    <row r="142" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D142" s="4"/>
     </row>
-    <row r="143" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B143" s="9"/>
       <c r="C143" s="9"/>
       <c r="D143" s="4"/>
     </row>
-    <row r="144" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D144" s="4"/>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B145" s="9"/>
       <c r="C145" s="9"/>
       <c r="D145" s="4"/>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D146" s="4"/>
     </row>
-    <row r="147" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B147" s="9"/>
       <c r="C147" s="9"/>
       <c r="D147" s="4"/>
     </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D148" s="4"/>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B149" s="9"/>
       <c r="C149" s="9"/>
       <c r="D149" s="4"/>
     </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D150" s="4"/>
     </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B151" s="9"/>
       <c r="C151" s="9"/>
       <c r="D151" s="4"/>
     </row>
-    <row r="152" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D152" s="4"/>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B153" s="9"/>
       <c r="C153" s="9"/>
       <c r="D153" s="4"/>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D154" s="4"/>
     </row>
-    <row r="155" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B155" s="9"/>
       <c r="C155" s="9"/>
       <c r="D155" s="4"/>
     </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D156" s="4"/>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B157" s="9"/>
       <c r="C157" s="9"/>
       <c r="D157" s="4"/>
     </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D158" s="4"/>
     </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B159" s="9"/>
       <c r="C159" s="9"/>
       <c r="D159" s="4"/>
     </row>
-    <row r="160" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D160" s="4"/>
     </row>
-    <row r="161" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B161" s="9"/>
       <c r="C161" s="9"/>
       <c r="D161" s="4"/>
     </row>
-    <row r="162" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D162" s="4"/>
     </row>
-    <row r="163" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B163" s="9"/>
       <c r="C163" s="9"/>
       <c r="D163" s="4"/>
     </row>
-    <row r="164" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D164" s="4"/>
     </row>
-    <row r="165" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B165" s="9"/>
       <c r="C165" s="9"/>
       <c r="D165" s="4"/>
     </row>
-    <row r="166" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D166" s="4"/>
     </row>
-    <row r="167" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B167" s="9"/>
       <c r="C167" s="9"/>
       <c r="D167" s="4"/>
     </row>
-    <row r="168" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D168" s="4"/>
     </row>
-    <row r="169" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B169" s="9"/>
       <c r="C169" s="9"/>
       <c r="D169" s="4"/>
     </row>
-    <row r="170" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D170" s="4"/>
     </row>
-    <row r="171" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B171" s="9"/>
       <c r="C171" s="9"/>
       <c r="D171" s="4"/>
     </row>
-    <row r="172" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D172" s="4"/>
     </row>
-    <row r="173" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B173" s="9"/>
       <c r="C173" s="9"/>
       <c r="D173" s="4"/>
     </row>
-    <row r="174" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D174" s="4"/>
     </row>
-    <row r="175" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B175" s="9"/>
       <c r="C175" s="9"/>
       <c r="D175" s="4"/>
     </row>
-    <row r="176" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D176" s="4"/>
     </row>
-    <row r="177" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B177" s="9"/>
       <c r="C177" s="9"/>
       <c r="D177" s="4"/>
     </row>
-    <row r="178" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D178" s="4"/>
     </row>
-    <row r="179" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B179" s="9"/>
       <c r="C179" s="9"/>
       <c r="D179" s="4"/>
     </row>
-    <row r="180" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D180" s="4"/>
     </row>
-    <row r="181" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B181" s="9"/>
       <c r="C181" s="9"/>
       <c r="D181" s="4"/>
     </row>
-    <row r="182" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D182" s="4"/>
     </row>
-    <row r="183" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B183" s="9"/>
       <c r="C183" s="9"/>
       <c r="D183" s="4"/>
     </row>
-    <row r="184" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D184" s="4"/>
     </row>
-    <row r="185" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B185" s="9"/>
       <c r="C185" s="9"/>
       <c r="D185" s="4"/>
     </row>
-    <row r="186" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D186" s="4"/>
     </row>
-    <row r="187" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B187" s="9"/>
       <c r="C187" s="9"/>
       <c r="D187" s="4"/>
     </row>
-    <row r="188" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D188" s="4"/>
     </row>
-    <row r="189" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B189" s="9"/>
       <c r="C189" s="9"/>
       <c r="D189" s="4"/>
     </row>
-    <row r="190" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D190" s="4"/>
     </row>
-    <row r="191" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B191" s="9"/>
       <c r="C191" s="9"/>
       <c r="D191" s="4"/>
     </row>
-    <row r="192" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D192" s="4"/>
     </row>
-    <row r="193" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B193" s="9"/>
       <c r="C193" s="9"/>
       <c r="D193" s="4"/>
     </row>
-    <row r="194" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D194" s="4"/>
     </row>
-    <row r="195" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B195" s="9"/>
       <c r="C195" s="9"/>
       <c r="D195" s="4"/>
     </row>
-    <row r="196" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D196" s="4"/>
     </row>
-    <row r="197" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B197" s="9"/>
       <c r="C197" s="9"/>
       <c r="D197" s="4"/>
     </row>
-    <row r="198" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D198" s="4"/>
     </row>
-    <row r="199" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B199" s="9"/>
       <c r="C199" s="9"/>
       <c r="D199" s="4"/>
     </row>
-    <row r="200" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D200" s="4"/>
     </row>
-    <row r="201" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B201" s="9"/>
       <c r="C201" s="9"/>
       <c r="D201" s="4"/>
     </row>
-    <row r="202" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D202" s="4"/>
     </row>
-    <row r="203" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B203" s="9"/>
       <c r="C203" s="9"/>
       <c r="D203" s="4"/>
     </row>
-    <row r="204" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D204" s="4"/>
     </row>
-    <row r="205" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B205" s="9"/>
       <c r="C205" s="9"/>
       <c r="D205" s="4"/>
     </row>
-    <row r="206" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D206" s="4"/>
     </row>
-    <row r="207" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B207" s="9"/>
       <c r="C207" s="9"/>
       <c r="D207" s="4"/>
     </row>
-    <row r="208" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D208" s="4"/>
     </row>
-    <row r="209" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B209" s="9"/>
       <c r="C209" s="9"/>
       <c r="D209" s="4"/>
     </row>
-    <row r="210" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D210" s="4"/>
     </row>
-    <row r="211" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B211" s="9"/>
       <c r="C211" s="9"/>
       <c r="D211" s="4"/>
     </row>
-    <row r="212" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D212" s="4"/>
     </row>
-    <row r="213" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B213" s="9"/>
       <c r="C213" s="9"/>
       <c r="D213" s="4"/>
     </row>
-    <row r="214" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D214" s="4"/>
     </row>
-    <row r="215" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B215" s="9"/>
       <c r="C215" s="9"/>
       <c r="D215" s="4"/>
     </row>
-    <row r="216" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D216" s="4"/>
     </row>
-    <row r="217" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B217" s="9"/>
       <c r="C217" s="9"/>
       <c r="D217" s="4"/>
     </row>
-    <row r="218" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D218" s="4"/>
     </row>
-    <row r="219" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B219" s="9"/>
       <c r="C219" s="9"/>
       <c r="D219" s="4"/>
     </row>
-    <row r="220" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D220" s="4"/>
     </row>
-    <row r="221" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B221" s="9"/>
       <c r="C221" s="9"/>
       <c r="D221" s="4"/>
     </row>
-    <row r="222" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D222" s="4"/>
     </row>
-    <row r="223" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B223" s="9"/>
       <c r="C223" s="9"/>
       <c r="D223" s="4"/>
     </row>
-    <row r="224" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D224" s="4"/>
     </row>
-    <row r="225" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B225" s="9"/>
       <c r="C225" s="9"/>
       <c r="D225" s="4"/>
     </row>
-    <row r="226" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D226" s="4"/>
     </row>
-    <row r="227" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B227" s="9"/>
       <c r="C227" s="9"/>
       <c r="D227" s="4"/>
     </row>
-    <row r="228" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D228" s="4"/>
     </row>
-    <row r="229" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B229" s="9"/>
       <c r="C229" s="9"/>
       <c r="D229" s="4"/>
     </row>
-    <row r="230" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D230" s="4"/>
     </row>
-    <row r="231" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B231" s="9"/>
       <c r="C231" s="9"/>
       <c r="D231" s="4"/>
     </row>
-    <row r="232" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D232" s="4"/>
     </row>
-    <row r="233" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B233" s="9"/>
       <c r="C233" s="9"/>
       <c r="D233" s="4"/>
     </row>
-    <row r="234" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D234" s="4"/>
     </row>
-    <row r="235" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B235" s="9"/>
       <c r="C235" s="9"/>
       <c r="D235" s="4"/>
     </row>
-    <row r="236" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D236" s="4"/>
     </row>
-    <row r="237" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B237" s="9"/>
       <c r="C237" s="9"/>
       <c r="D237" s="4"/>
     </row>
-    <row r="238" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D238" s="4"/>
     </row>
-    <row r="239" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B239" s="9"/>
       <c r="C239" s="9"/>
       <c r="D239" s="4"/>
     </row>
-    <row r="240" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D240" s="4"/>
     </row>
-    <row r="241" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B241" s="9"/>
       <c r="C241" s="9"/>
       <c r="D241" s="4"/>
     </row>
-    <row r="242" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D242" s="4"/>
     </row>
-    <row r="243" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B243" s="9"/>
       <c r="C243" s="9"/>
       <c r="D243" s="4"/>
     </row>
-    <row r="244" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D244" s="4"/>
     </row>
-    <row r="245" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B245" s="9"/>
       <c r="C245" s="9"/>
       <c r="D245" s="4"/>
     </row>
-    <row r="246" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D246" s="4"/>
     </row>
-    <row r="247" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B247" s="9"/>
       <c r="C247" s="9"/>
       <c r="D247" s="4"/>
     </row>
-    <row r="248" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D248" s="4"/>
     </row>
-    <row r="249" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B249" s="9"/>
       <c r="C249" s="9"/>
       <c r="D249" s="4"/>
     </row>
-    <row r="250" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D250" s="4"/>
     </row>
-    <row r="251" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B251" s="9"/>
       <c r="C251" s="9"/>
       <c r="D251" s="4"/>
     </row>
-    <row r="252" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D252" s="4"/>
     </row>
-    <row r="253" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B253" s="9"/>
       <c r="C253" s="9"/>
       <c r="D253" s="4"/>
     </row>
-    <row r="254" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D254" s="4"/>
     </row>
-    <row r="255" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B255" s="9"/>
       <c r="C255" s="9"/>
       <c r="D255" s="4"/>
     </row>
-    <row r="256" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D256" s="4"/>
     </row>
-    <row r="257" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B257" s="9"/>
       <c r="C257" s="9"/>
       <c r="D257" s="4"/>
     </row>
-    <row r="258" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D258" s="4"/>
     </row>
-    <row r="259" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B259" s="9"/>
       <c r="C259" s="9"/>
       <c r="D259" s="4"/>
     </row>
-    <row r="260" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D260" s="4"/>
     </row>
-    <row r="261" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B261" s="9"/>
       <c r="C261" s="9"/>
       <c r="D261" s="4"/>
     </row>
-    <row r="262" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D262" s="4"/>
     </row>
-    <row r="263" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B263" s="9"/>
       <c r="C263" s="9"/>
       <c r="D263" s="4"/>
     </row>
-    <row r="264" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D264" s="4"/>
     </row>
-    <row r="265" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B265" s="9"/>
       <c r="C265" s="9"/>
       <c r="D265" s="4"/>
     </row>
-    <row r="266" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D266" s="4"/>
     </row>
-    <row r="267" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B267" s="9"/>
       <c r="C267" s="9"/>
       <c r="D267" s="4"/>
     </row>
-    <row r="268" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D268" s="4"/>
     </row>
-    <row r="269" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B269" s="9"/>
       <c r="C269" s="9"/>
       <c r="D269" s="4"/>
     </row>
-    <row r="270" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D270" s="4"/>
     </row>
-    <row r="271" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B271" s="9"/>
       <c r="C271" s="9"/>
       <c r="D271" s="4"/>
     </row>
-    <row r="272" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D272" s="4"/>
     </row>
-    <row r="273" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B273" s="9"/>
       <c r="C273" s="9"/>
       <c r="D273" s="4"/>
     </row>
-    <row r="274" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D274" s="4"/>
     </row>
-    <row r="275" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B275" s="9"/>
       <c r="C275" s="9"/>
       <c r="D275" s="4"/>
     </row>
-    <row r="276" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D276" s="4"/>
     </row>
-    <row r="277" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B277" s="9"/>
       <c r="C277" s="9"/>
       <c r="D277" s="4"/>
     </row>
-    <row r="278" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D278" s="4"/>
     </row>
-    <row r="279" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B279" s="9"/>
       <c r="C279" s="9"/>
       <c r="D279" s="4"/>
     </row>
-    <row r="280" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D280" s="4"/>
     </row>
-    <row r="281" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B281" s="9"/>
       <c r="C281" s="9"/>
       <c r="D281" s="4"/>
     </row>
-    <row r="282" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D282" s="4"/>
     </row>
-    <row r="283" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B283" s="9"/>
       <c r="C283" s="9"/>
       <c r="D283" s="4"/>
     </row>
-    <row r="284" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D284" s="4"/>
     </row>
-    <row r="285" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B285" s="9"/>
       <c r="C285" s="9"/>
       <c r="D285" s="4"/>
     </row>
-    <row r="286" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D286" s="4"/>
     </row>
-    <row r="287" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B287" s="9"/>
       <c r="C287" s="9"/>
       <c r="D287" s="4"/>
     </row>
-    <row r="288" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D288" s="4"/>
     </row>
-    <row r="289" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B289" s="9"/>
       <c r="C289" s="9"/>
       <c r="D289" s="4"/>
     </row>
-    <row r="290" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D290" s="4"/>
     </row>
-    <row r="291" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B291" s="9"/>
       <c r="C291" s="9"/>
       <c r="D291" s="4"/>
     </row>
-    <row r="292" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D292" s="4"/>
     </row>
-    <row r="293" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B293" s="9"/>
       <c r="C293" s="9"/>
       <c r="D293" s="4"/>
     </row>
-    <row r="294" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D294" s="4"/>
     </row>
-    <row r="295" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B295" s="9"/>
       <c r="C295" s="9"/>
       <c r="D295" s="4"/>
     </row>
-    <row r="296" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D296" s="4"/>
     </row>
-    <row r="297" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B297" s="9"/>
       <c r="C297" s="9"/>
       <c r="D297" s="4"/>
     </row>
-    <row r="298" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D298" s="4"/>
     </row>
-    <row r="299" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B299" s="9"/>
       <c r="C299" s="9"/>
       <c r="D299" s="4"/>
     </row>
-    <row r="300" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D300" s="4"/>
     </row>
-    <row r="301" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B301" s="9"/>
       <c r="C301" s="9"/>
       <c r="D301" s="4"/>
     </row>
-    <row r="302" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D302" s="4"/>
     </row>
-    <row r="303" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B303" s="9"/>
       <c r="C303" s="9"/>
       <c r="D303" s="4"/>
     </row>
-    <row r="304" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D304" s="4"/>
     </row>
-    <row r="305" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B305" s="9"/>
       <c r="C305" s="9"/>
       <c r="D305" s="4"/>
     </row>
-    <row r="306" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D306" s="4"/>
     </row>
-    <row r="307" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B307" s="9"/>
       <c r="C307" s="9"/>
       <c r="D307" s="4"/>
     </row>
-    <row r="308" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D308" s="4"/>
     </row>
-    <row r="309" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B309" s="9"/>
       <c r="C309" s="9"/>
       <c r="D309" s="4"/>
     </row>
-    <row r="310" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D310" s="4"/>
     </row>
-    <row r="311" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B311" s="9"/>
       <c r="C311" s="9"/>
       <c r="D311" s="4"/>
     </row>
-    <row r="312" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D312" s="4"/>
     </row>
-    <row r="313" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B313" s="9"/>
       <c r="C313" s="9"/>
       <c r="D313" s="4"/>
     </row>
-    <row r="314" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D314" s="4"/>
     </row>
-    <row r="315" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B315" s="9"/>
       <c r="C315" s="9"/>
       <c r="D315" s="4"/>
     </row>
-    <row r="316" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D316" s="4"/>
     </row>
-    <row r="317" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B317" s="9"/>
       <c r="C317" s="9"/>
       <c r="D317" s="4"/>
     </row>
-    <row r="318" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D318" s="4"/>
     </row>
-    <row r="319" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B319" s="9"/>
       <c r="C319" s="9"/>
       <c r="D319" s="4"/>
     </row>
-    <row r="320" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D320" s="4"/>
     </row>
-    <row r="321" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B321" s="9"/>
       <c r="C321" s="9"/>
       <c r="D321" s="4"/>
     </row>
-    <row r="322" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="322" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D322" s="4"/>
     </row>
-    <row r="323" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="323" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B323" s="9"/>
       <c r="C323" s="9"/>
       <c r="D323" s="4"/>
     </row>
-    <row r="324" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="324" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D324" s="4"/>
     </row>
-    <row r="325" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B325" s="9"/>
       <c r="C325" s="9"/>
       <c r="D325" s="4"/>
     </row>
-    <row r="326" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="326" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D326" s="4"/>
     </row>
-    <row r="327" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="327" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B327" s="9"/>
       <c r="C327" s="9"/>
       <c r="D327" s="4"/>
     </row>
-    <row r="328" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="328" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D328" s="4"/>
     </row>
-    <row r="329" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="329" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B329" s="9"/>
       <c r="C329" s="9"/>
       <c r="D329" s="4"/>
     </row>
-    <row r="330" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="330" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D330" s="4"/>
     </row>
-    <row r="331" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="331" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B331" s="9"/>
       <c r="C331" s="9"/>
       <c r="D331" s="4"/>
     </row>
-    <row r="332" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="332" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D332" s="4"/>
     </row>
-    <row r="333" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="333" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B333" s="9"/>
       <c r="C333" s="9"/>
       <c r="D333" s="4"/>
     </row>
-    <row r="334" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="334" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D334" s="4"/>
     </row>
-    <row r="335" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="335" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B335" s="9"/>
       <c r="C335" s="9"/>
       <c r="D335" s="4"/>
     </row>
-    <row r="336" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D336" s="4"/>
     </row>
-    <row r="337" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="337" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B337" s="9"/>
       <c r="C337" s="9"/>
       <c r="D337" s="4"/>
     </row>
-    <row r="338" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D338" s="4"/>
     </row>
-    <row r="339" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="339" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B339" s="9"/>
       <c r="C339" s="9"/>
       <c r="D339" s="4"/>
     </row>
-    <row r="340" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="340" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D340" s="4"/>
     </row>
-    <row r="341" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="341" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B341" s="9"/>
       <c r="C341" s="9"/>
       <c r="D341" s="4"/>
     </row>
-    <row r="342" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="342" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D342" s="4"/>
     </row>
-    <row r="343" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="343" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B343" s="9"/>
       <c r="C343" s="9"/>
       <c r="D343" s="4"/>
     </row>
-    <row r="344" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="344" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D344" s="4"/>
     </row>
-    <row r="345" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B345" s="9"/>
       <c r="C345" s="9"/>
       <c r="D345" s="4"/>
     </row>
-    <row r="346" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="346" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D346" s="4"/>
     </row>
-    <row r="347" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B347" s="9"/>
       <c r="C347" s="9"/>
       <c r="D347" s="4"/>
     </row>
-    <row r="348" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="348" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D348" s="4"/>
     </row>
-    <row r="349" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B349" s="9"/>
       <c r="C349" s="9"/>
       <c r="D349" s="4"/>
     </row>
-    <row r="350" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D350" s="4"/>
     </row>
-    <row r="351" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="351" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B351" s="9"/>
       <c r="C351" s="9"/>
       <c r="D351" s="4"/>
     </row>
-    <row r="352" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D352" s="4"/>
     </row>
-    <row r="353" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="353" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B353" s="9"/>
       <c r="C353" s="9"/>
       <c r="D353" s="4"/>
     </row>
-    <row r="354" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D354" s="4"/>
     </row>
-    <row r="355" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B355" s="9"/>
       <c r="C355" s="9"/>
       <c r="D355" s="4"/>
     </row>
-    <row r="356" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D356" s="4"/>
     </row>
-    <row r="357" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="357" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B357" s="9"/>
       <c r="C357" s="9"/>
       <c r="D357" s="4"/>
     </row>
-    <row r="358" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="358" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D358" s="4"/>
     </row>
-    <row r="359" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="359" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B359" s="9"/>
       <c r="C359" s="9"/>
       <c r="D359" s="4"/>
     </row>
-    <row r="360" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="360" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D360" s="4"/>
     </row>
-    <row r="361" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="361" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B361" s="9"/>
       <c r="C361" s="9"/>
       <c r="D361" s="4"/>
     </row>
-    <row r="362" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="362" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D362" s="4"/>
     </row>
-    <row r="363" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="363" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B363" s="9"/>
       <c r="C363" s="9"/>
       <c r="D363" s="4"/>
     </row>
-    <row r="364" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="364" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D364" s="4"/>
     </row>
-    <row r="365" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="365" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B365" s="9"/>
       <c r="C365" s="9"/>
       <c r="D365" s="4"/>
     </row>
-    <row r="366" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="366" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D366" s="4"/>
     </row>
-    <row r="367" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="367" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B367" s="9"/>
       <c r="C367" s="9"/>
       <c r="D367" s="4"/>
     </row>
-    <row r="368" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="368" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D368" s="4"/>
     </row>
-    <row r="369" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="369" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B369" s="9"/>
       <c r="C369" s="9"/>
       <c r="D369" s="4"/>
     </row>
-    <row r="370" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="370" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D370" s="4"/>
     </row>
-    <row r="371" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="371" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B371" s="9"/>
       <c r="C371" s="9"/>
       <c r="D371" s="4"/>
     </row>
-    <row r="372" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D372" s="4"/>
     </row>
-    <row r="373" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="373" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B373" s="9"/>
       <c r="C373" s="9"/>
       <c r="D373" s="4"/>
     </row>
-    <row r="374" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="374" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D374" s="4"/>
     </row>
-    <row r="375" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="375" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B375" s="9"/>
       <c r="C375" s="9"/>
       <c r="D375" s="4"/>
     </row>
-    <row r="376" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="376" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D376" s="4"/>
     </row>
-    <row r="377" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="377" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B377" s="9"/>
       <c r="C377" s="9"/>
       <c r="D377" s="4"/>
     </row>
-    <row r="378" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="378" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D378" s="4"/>
     </row>
-    <row r="379" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="379" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B379" s="9"/>
       <c r="C379" s="9"/>
       <c r="D379" s="4"/>
     </row>
-    <row r="380" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="380" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D380" s="4"/>
     </row>
-    <row r="381" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="381" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B381" s="9"/>
       <c r="C381" s="9"/>
       <c r="D381" s="4"/>
     </row>
-    <row r="382" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D382" s="4"/>
     </row>
-    <row r="383" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="383" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B383" s="9"/>
       <c r="C383" s="9"/>
       <c r="D383" s="4"/>
     </row>
-    <row r="384" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="384" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D384" s="4"/>
     </row>
-    <row r="385" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="385" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B385" s="9"/>
       <c r="C385" s="9"/>
       <c r="D385" s="4"/>
     </row>
-    <row r="386" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="386" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D386" s="4"/>
     </row>
-    <row r="387" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="387" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B387" s="9"/>
       <c r="C387" s="9"/>
       <c r="D387" s="4"/>
     </row>
-    <row r="388" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="388" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D388" s="4"/>
     </row>
-    <row r="389" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="389" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B389" s="9"/>
       <c r="C389" s="9"/>
       <c r="D389" s="4"/>
     </row>
-    <row r="390" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="390" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D390" s="4"/>
     </row>
-    <row r="391" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="391" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B391" s="9"/>
       <c r="C391" s="9"/>
       <c r="D391" s="4"/>
     </row>
-    <row r="392" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="392" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D392" s="4"/>
     </row>
-    <row r="393" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="393" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B393" s="9"/>
       <c r="C393" s="9"/>
       <c r="D393" s="4"/>
     </row>
-    <row r="394" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="394" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D394" s="4"/>
     </row>
-    <row r="395" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="395" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B395" s="9"/>
       <c r="C395" s="9"/>
       <c r="D395" s="4"/>
     </row>
-    <row r="396" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="396" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D396" s="4"/>
     </row>
-    <row r="397" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="397" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B397" s="9"/>
       <c r="C397" s="9"/>
       <c r="D397" s="4"/>
     </row>
-    <row r="398" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="398" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D398" s="4"/>
     </row>
-    <row r="399" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="399" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B399" s="9"/>
       <c r="C399" s="9"/>
       <c r="D399" s="4"/>
     </row>
-    <row r="400" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="400" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D400" s="4"/>
     </row>
-    <row r="401" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="401" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B401" s="9"/>
       <c r="C401" s="9"/>
       <c r="D401" s="4"/>
     </row>
-    <row r="402" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="402" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D402" s="4"/>
     </row>
-    <row r="403" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="403" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B403" s="9"/>
       <c r="C403" s="9"/>
       <c r="D403" s="4"/>
     </row>
-    <row r="404" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="404" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D404" s="4"/>
     </row>
-    <row r="405" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="405" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B405" s="9"/>
       <c r="C405" s="9"/>
       <c r="D405" s="4"/>
     </row>
-    <row r="406" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="406" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D406" s="4"/>
     </row>
-    <row r="407" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="407" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B407" s="9"/>
       <c r="C407" s="9"/>
       <c r="D407" s="4"/>
     </row>
-    <row r="408" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="408" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D408" s="4"/>
     </row>
-    <row r="409" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="409" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B409" s="9"/>
       <c r="C409" s="9"/>
       <c r="D409" s="4"/>
     </row>
-    <row r="410" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="410" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D410" s="4"/>
     </row>
-    <row r="411" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="411" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B411" s="9"/>
       <c r="C411" s="9"/>
       <c r="D411" s="4"/>
     </row>
-    <row r="412" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="412" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D412" s="4"/>
     </row>
-    <row r="413" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="413" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B413" s="9"/>
       <c r="C413" s="9"/>
       <c r="D413" s="4"/>
     </row>
-    <row r="414" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="414" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D414" s="4"/>
     </row>
-    <row r="415" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="415" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B415" s="9"/>
       <c r="C415" s="9"/>
       <c r="D415" s="4"/>
     </row>
-    <row r="416" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="416" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D416" s="4"/>
     </row>
-    <row r="417" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="417" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B417" s="9"/>
       <c r="C417" s="9"/>
       <c r="D417" s="4"/>
     </row>
-    <row r="418" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="418" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D418" s="4"/>
     </row>
-    <row r="419" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="419" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B419" s="9"/>
       <c r="C419" s="9"/>
       <c r="D419" s="4"/>
     </row>
-    <row r="420" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="420" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D420" s="4"/>
     </row>
-    <row r="421" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="421" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B421" s="9"/>
       <c r="C421" s="9"/>
       <c r="D421" s="4"/>
     </row>
-    <row r="422" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="422" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D422" s="4"/>
     </row>
-    <row r="423" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="423" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B423" s="9"/>
       <c r="C423" s="9"/>
       <c r="D423" s="4"/>
     </row>
-    <row r="424" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="424" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D424" s="4"/>
     </row>
-    <row r="425" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="425" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B425" s="9"/>
       <c r="C425" s="9"/>
       <c r="D425" s="4"/>
     </row>
-    <row r="426" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="426" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D426" s="4"/>
     </row>
-    <row r="427" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="427" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B427" s="9"/>
       <c r="C427" s="9"/>
       <c r="D427" s="4"/>
     </row>
-    <row r="428" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="428" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D428" s="4"/>
     </row>
-    <row r="429" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="429" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B429" s="9"/>
       <c r="C429" s="9"/>
       <c r="D429" s="4"/>
     </row>
-    <row r="430" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="430" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D430" s="4"/>
     </row>
-    <row r="431" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="431" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B431" s="9"/>
       <c r="C431" s="9"/>
       <c r="D431" s="4"/>
     </row>
-    <row r="432" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="432" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D432" s="4"/>
     </row>
-    <row r="433" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A433" s="7"/>
       <c r="B433" s="9"/>
       <c r="C433" s="9"/>
     </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B434" s="9"/>
       <c r="C434" s="9"/>
     </row>
-    <row r="435" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A435" s="7"/>
       <c r="B435" s="9"/>
       <c r="C435" s="9"/>
     </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B436" s="9"/>
       <c r="C436" s="9"/>
     </row>
-    <row r="437" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A437" s="7"/>
       <c r="B437" s="9"/>
       <c r="C437" s="9"/>
     </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B438" s="9"/>
       <c r="C438" s="9"/>
     </row>
-    <row r="439" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A439" s="7"/>
       <c r="B439" s="9"/>
       <c r="C439" s="9"/>
     </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B440" s="9"/>
       <c r="C440" s="9"/>
     </row>
-    <row r="441" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A441" s="7"/>
       <c r="B441" s="9"/>
       <c r="C441" s="9"/>
     </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B442" s="9"/>
       <c r="C442" s="9"/>
     </row>
-    <row r="443" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A443" s="7"/>
       <c r="B443" s="9"/>
       <c r="C443" s="9"/>
     </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B444" s="9"/>
       <c r="C444" s="9"/>
     </row>
-    <row r="445" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A445" s="7"/>
       <c r="B445" s="9"/>
       <c r="C445" s="9"/>
     </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B446" s="9"/>
       <c r="C446" s="9"/>
     </row>
-    <row r="447" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A447" s="7"/>
       <c r="B447" s="9"/>
       <c r="C447" s="9"/>
     </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B448" s="9"/>
       <c r="C448" s="9"/>
     </row>
-    <row r="449" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A449" s="7"/>
       <c r="B449" s="9"/>
       <c r="C449" s="9"/>
     </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B450" s="9"/>
       <c r="C450" s="9"/>
     </row>
-    <row r="451" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A451" s="7"/>
       <c r="B451" s="9"/>
       <c r="C451" s="9"/>
     </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B452" s="9"/>
       <c r="C452" s="9"/>
     </row>
-    <row r="453" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A453" s="7"/>
       <c r="B453" s="9"/>
       <c r="C453" s="9"/>
     </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B454" s="9"/>
       <c r="C454" s="9"/>
     </row>
-    <row r="455" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A455" s="7"/>
       <c r="B455" s="9"/>
       <c r="C455" s="9"/>
     </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B456" s="9"/>
       <c r="C456" s="9"/>
     </row>
-    <row r="457" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A457" s="7"/>
       <c r="B457" s="9"/>
       <c r="C457" s="9"/>
     </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B458" s="9"/>
       <c r="C458" s="9"/>
     </row>
-    <row r="459" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A459" s="7"/>
       <c r="B459" s="9"/>
       <c r="C459" s="9"/>
     </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B460" s="9"/>
       <c r="C460" s="9"/>
     </row>
-    <row r="461" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A461" s="7"/>
       <c r="B461" s="9"/>
       <c r="C461" s="9"/>
     </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B462" s="9"/>
       <c r="C462" s="9"/>
     </row>
-    <row r="463" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A463" s="7"/>
       <c r="B463" s="9"/>
       <c r="C463" s="9"/>
     </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B464" s="9"/>
       <c r="C464" s="9"/>
     </row>
-    <row r="465" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A465" s="7"/>
       <c r="B465" s="9"/>
       <c r="C465" s="9"/>
     </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B466" s="9"/>
       <c r="C466" s="9"/>
     </row>
-    <row r="467" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A467" s="7"/>
       <c r="B467" s="9"/>
       <c r="C467" s="9"/>
     </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B468" s="9"/>
       <c r="C468" s="9"/>
     </row>
-    <row r="469" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A469" s="7"/>
       <c r="B469" s="9"/>
       <c r="C469" s="9"/>
     </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B470" s="9"/>
       <c r="C470" s="9"/>
     </row>
-    <row r="471" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A471" s="7"/>
       <c r="B471" s="9"/>
       <c r="C471" s="9"/>
     </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B472" s="9"/>
       <c r="C472" s="9"/>
     </row>
-    <row r="473" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A473" s="7"/>
       <c r="B473" s="9"/>
       <c r="C473" s="9"/>
     </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B474" s="9"/>
       <c r="C474" s="9"/>
     </row>
-    <row r="475" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A475" s="7"/>
       <c r="B475" s="9"/>
       <c r="C475" s="9"/>
     </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B476" s="9"/>
       <c r="C476" s="9"/>
     </row>
-    <row r="477" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A477" s="7"/>
       <c r="B477" s="9"/>
       <c r="C477" s="9"/>
     </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B478" s="9"/>
       <c r="C478" s="9"/>
     </row>
-    <row r="479" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A479" s="7"/>
       <c r="B479" s="9"/>
       <c r="C479" s="9"/>
     </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B480" s="9"/>
       <c r="C480" s="9"/>
     </row>
-    <row r="481" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A481" s="7"/>
       <c r="B481" s="9"/>
       <c r="C481" s="9"/>
     </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B482" s="9"/>
       <c r="C482" s="9"/>
     </row>
-    <row r="483" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A483" s="7"/>
       <c r="B483" s="9"/>
       <c r="C483" s="9"/>
     </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B484" s="9"/>
       <c r="C484" s="9"/>
     </row>
-    <row r="485" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A485" s="7"/>
       <c r="B485" s="9"/>
       <c r="C485" s="9"/>
     </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B486" s="9"/>
       <c r="C486" s="9"/>
     </row>
-    <row r="487" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A487" s="7"/>
       <c r="B487" s="9"/>
       <c r="C487" s="9"/>
     </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B488" s="9"/>
       <c r="C488" s="9"/>
     </row>
-    <row r="489" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A489" s="7"/>
       <c r="B489" s="9"/>
       <c r="C489" s="9"/>
     </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B490" s="9"/>
       <c r="C490" s="9"/>
     </row>
-    <row r="491" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A491" s="7"/>
       <c r="B491" s="9"/>
     </row>
-    <row r="493" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A493" s="7"/>
     </row>
-    <row r="495" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A495" s="7"/>
     </row>
   </sheetData>
@@ -4922,15 +4922,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A406477-0BDC-404F-93CF-7E7D1F43F43F}">
   <dimension ref="A1:D670"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" style="10" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" customWidth="1"/>
+    <col min="1" max="1" width="14.54296875" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" style="10" customWidth="1"/>
+    <col min="4" max="4" width="17.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>22</v>
       </c>
@@ -4941,7 +4941,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -4952,7 +4952,7 @@
         <v>24.591899999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -4964,7 +4964,7 @@
       </c>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="D8" s="4"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="D10" s="4"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="D12" s="4"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -5096,7 +5096,7 @@
       </c>
       <c r="D14" s="4"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="D16" s="4"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="D18" s="4"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="D20" s="4"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="D22" s="4"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>13</v>
       </c>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="D24" s="4"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>7</v>
       </c>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="D26" s="4"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>13</v>
       </c>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="D27" s="4"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>7</v>
       </c>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="D28" s="4"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>13</v>
       </c>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="D29" s="4"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="D30" s="4"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>13</v>
       </c>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>7</v>
       </c>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="D32" s="4"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>13</v>
       </c>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>7</v>
       </c>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="D34" s="4"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>13</v>
       </c>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="D35" s="4"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>7</v>
       </c>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="D36" s="4"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>13</v>
       </c>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="D37" s="4"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>7</v>
       </c>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="D38" s="4"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>13</v>
       </c>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>7</v>
       </c>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="D40" s="4"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>13</v>
       </c>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="D41" s="4"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>7</v>
       </c>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="D42" s="4"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>13</v>
       </c>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="D43" s="4"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>7</v>
       </c>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="D44" s="4"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>13</v>
       </c>
@@ -5468,7 +5468,7 @@
       </c>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>7</v>
       </c>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="D46" s="4"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>13</v>
       </c>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="D47" s="4"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>7</v>
       </c>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="D48" s="4"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>13</v>
       </c>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="D49" s="4"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>7</v>
       </c>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D50" s="4"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>13</v>
       </c>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="D51" s="4"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="D52" s="4"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>13</v>
       </c>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="D53" s="4"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>7</v>
       </c>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="D54" s="4"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>13</v>
       </c>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="D55" s="4"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>7</v>
       </c>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>13</v>
       </c>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="D57" s="4"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -5624,7 +5624,7 @@
       </c>
       <c r="D58" s="4"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>13</v>
       </c>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="D59" s="4"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>7</v>
       </c>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="D60" s="4"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>13</v>
       </c>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="D61" s="4"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>7</v>
       </c>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="D62" s="4"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>13</v>
       </c>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="D63" s="4"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>7</v>
       </c>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="D64" s="4"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>13</v>
       </c>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="D65" s="4"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>7</v>
       </c>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="D66" s="4"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>13</v>
       </c>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="D67" s="4"/>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>7</v>
       </c>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="D68" s="4"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>13</v>
       </c>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="D69" s="4"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>7</v>
       </c>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="D70" s="4"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>13</v>
       </c>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="D71" s="4"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>7</v>
       </c>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="D72" s="4"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>13</v>
       </c>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="D73" s="4"/>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>7</v>
       </c>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="D74" s="4"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>13</v>
       </c>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="D75" s="4"/>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>7</v>
       </c>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="D76" s="4"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>13</v>
       </c>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="D77" s="4"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>7</v>
       </c>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="D78" s="4"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>13</v>
       </c>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="D79" s="4"/>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>7</v>
       </c>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="D80" s="4"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>13</v>
       </c>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="D81" s="4"/>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>7</v>
       </c>
@@ -5912,2206 +5912,2206 @@
       </c>
       <c r="D82" s="4"/>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B83" s="9"/>
       <c r="C83" s="9"/>
       <c r="D83" s="4"/>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D84" s="4"/>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B85" s="9"/>
       <c r="C85" s="9"/>
       <c r="D85" s="4"/>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D86" s="4"/>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B87" s="9"/>
       <c r="C87" s="9"/>
       <c r="D87" s="4"/>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D88" s="4"/>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B89" s="9"/>
       <c r="C89" s="9"/>
       <c r="D89" s="4"/>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D90" s="4"/>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B91" s="9"/>
       <c r="C91" s="9"/>
       <c r="D91" s="4"/>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D92" s="4"/>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B93" s="9"/>
       <c r="C93" s="9"/>
       <c r="D93" s="4"/>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D94" s="4"/>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B95" s="9"/>
       <c r="C95" s="9"/>
       <c r="D95" s="4"/>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D96" s="4"/>
     </row>
-    <row r="97" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B97" s="9"/>
       <c r="C97" s="9"/>
       <c r="D97" s="4"/>
     </row>
-    <row r="98" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D98" s="4"/>
     </row>
-    <row r="99" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B99" s="9"/>
       <c r="C99" s="9"/>
       <c r="D99" s="4"/>
     </row>
-    <row r="100" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D100" s="4"/>
     </row>
-    <row r="101" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B101" s="9"/>
       <c r="C101" s="9"/>
       <c r="D101" s="4"/>
     </row>
-    <row r="102" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D102" s="4"/>
     </row>
-    <row r="103" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B103" s="9"/>
       <c r="C103" s="9"/>
       <c r="D103" s="4"/>
     </row>
-    <row r="104" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D104" s="4"/>
     </row>
-    <row r="105" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B105" s="9"/>
       <c r="C105" s="9"/>
       <c r="D105" s="4"/>
     </row>
-    <row r="106" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D106" s="4"/>
     </row>
-    <row r="107" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B107" s="9"/>
       <c r="C107" s="9"/>
       <c r="D107" s="4"/>
     </row>
-    <row r="108" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D108" s="4"/>
     </row>
-    <row r="109" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B109" s="9"/>
       <c r="C109" s="9"/>
       <c r="D109" s="4"/>
     </row>
-    <row r="110" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D110" s="4"/>
     </row>
-    <row r="111" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B111" s="9"/>
       <c r="C111" s="9"/>
       <c r="D111" s="4"/>
     </row>
-    <row r="112" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D112" s="4"/>
     </row>
-    <row r="113" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B113" s="9"/>
       <c r="C113" s="9"/>
       <c r="D113" s="4"/>
     </row>
-    <row r="114" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D114" s="4"/>
     </row>
-    <row r="115" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B115" s="9"/>
       <c r="C115" s="9"/>
       <c r="D115" s="4"/>
     </row>
-    <row r="116" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D116" s="4"/>
     </row>
-    <row r="117" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B117" s="9"/>
       <c r="C117" s="9"/>
       <c r="D117" s="4"/>
     </row>
-    <row r="118" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D118" s="4"/>
     </row>
-    <row r="119" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B119" s="9"/>
       <c r="C119" s="9"/>
       <c r="D119" s="4"/>
     </row>
-    <row r="120" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D120" s="4"/>
     </row>
-    <row r="121" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B121" s="9"/>
       <c r="C121" s="9"/>
       <c r="D121" s="4"/>
     </row>
-    <row r="122" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D122" s="4"/>
     </row>
-    <row r="123" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B123" s="9"/>
       <c r="C123" s="9"/>
       <c r="D123" s="4"/>
     </row>
-    <row r="124" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D124" s="4"/>
     </row>
-    <row r="125" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B125" s="9"/>
       <c r="C125" s="9"/>
       <c r="D125" s="4"/>
     </row>
-    <row r="126" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D126" s="4"/>
     </row>
-    <row r="127" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B127" s="9"/>
       <c r="C127" s="9"/>
       <c r="D127" s="4"/>
     </row>
-    <row r="128" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D128" s="4"/>
     </row>
-    <row r="129" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B129" s="9"/>
       <c r="C129" s="9"/>
       <c r="D129" s="4"/>
     </row>
-    <row r="130" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D130" s="4"/>
     </row>
-    <row r="131" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B131" s="9"/>
       <c r="C131" s="9"/>
       <c r="D131" s="4"/>
     </row>
-    <row r="132" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D132" s="4"/>
     </row>
-    <row r="133" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B133" s="9"/>
       <c r="C133" s="9"/>
       <c r="D133" s="4"/>
     </row>
-    <row r="134" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D134" s="4"/>
     </row>
-    <row r="135" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B135" s="9"/>
       <c r="C135" s="9"/>
       <c r="D135" s="4"/>
     </row>
-    <row r="136" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D136" s="4"/>
     </row>
-    <row r="137" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B137" s="9"/>
       <c r="C137" s="9"/>
       <c r="D137" s="4"/>
     </row>
-    <row r="138" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D138" s="4"/>
     </row>
-    <row r="139" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B139" s="9"/>
       <c r="C139" s="9"/>
       <c r="D139" s="4"/>
     </row>
-    <row r="140" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D140" s="4"/>
     </row>
-    <row r="141" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B141" s="9"/>
       <c r="C141" s="9"/>
       <c r="D141" s="4"/>
     </row>
-    <row r="142" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D142" s="4"/>
     </row>
-    <row r="143" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B143" s="9"/>
       <c r="C143" s="9"/>
       <c r="D143" s="4"/>
     </row>
-    <row r="144" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D144" s="4"/>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B145" s="9"/>
       <c r="C145" s="9"/>
       <c r="D145" s="4"/>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D146" s="4"/>
     </row>
-    <row r="147" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B147" s="9"/>
       <c r="C147" s="9"/>
       <c r="D147" s="4"/>
     </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D148" s="4"/>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B149" s="9"/>
       <c r="C149" s="9"/>
       <c r="D149" s="4"/>
     </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D150" s="4"/>
     </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B151" s="9"/>
       <c r="C151" s="9"/>
       <c r="D151" s="4"/>
     </row>
-    <row r="152" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D152" s="4"/>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B153" s="9"/>
       <c r="C153" s="9"/>
       <c r="D153" s="4"/>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D154" s="4"/>
     </row>
-    <row r="155" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B155" s="9"/>
       <c r="C155" s="9"/>
       <c r="D155" s="4"/>
     </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D156" s="4"/>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B157" s="9"/>
       <c r="C157" s="9"/>
       <c r="D157" s="4"/>
     </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D158" s="4"/>
     </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B159" s="9"/>
       <c r="C159" s="9"/>
       <c r="D159" s="4"/>
     </row>
-    <row r="160" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D160" s="4"/>
     </row>
-    <row r="161" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B161" s="9"/>
       <c r="C161" s="9"/>
       <c r="D161" s="4"/>
     </row>
-    <row r="162" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D162" s="4"/>
     </row>
-    <row r="163" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B163" s="9"/>
       <c r="C163" s="9"/>
       <c r="D163" s="4"/>
     </row>
-    <row r="164" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D164" s="4"/>
     </row>
-    <row r="165" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B165" s="9"/>
       <c r="C165" s="9"/>
       <c r="D165" s="4"/>
     </row>
-    <row r="166" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D166" s="4"/>
     </row>
-    <row r="167" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B167" s="9"/>
       <c r="C167" s="9"/>
       <c r="D167" s="4"/>
     </row>
-    <row r="168" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D168" s="4"/>
     </row>
-    <row r="169" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B169" s="9"/>
       <c r="C169" s="9"/>
       <c r="D169" s="4"/>
     </row>
-    <row r="170" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D170" s="4"/>
     </row>
-    <row r="171" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B171" s="9"/>
       <c r="C171" s="9"/>
       <c r="D171" s="4"/>
     </row>
-    <row r="172" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D172" s="4"/>
     </row>
-    <row r="173" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B173" s="9"/>
       <c r="C173" s="9"/>
       <c r="D173" s="4"/>
     </row>
-    <row r="174" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D174" s="4"/>
     </row>
-    <row r="175" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B175" s="9"/>
       <c r="C175" s="9"/>
       <c r="D175" s="4"/>
     </row>
-    <row r="176" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D176" s="4"/>
     </row>
-    <row r="177" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B177" s="9"/>
       <c r="C177" s="9"/>
       <c r="D177" s="4"/>
     </row>
-    <row r="178" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D178" s="4"/>
     </row>
-    <row r="179" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B179" s="9"/>
       <c r="C179" s="9"/>
       <c r="D179" s="4"/>
     </row>
-    <row r="180" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D180" s="4"/>
     </row>
-    <row r="181" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B181" s="9"/>
       <c r="C181" s="9"/>
       <c r="D181" s="4"/>
     </row>
-    <row r="182" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D182" s="4"/>
     </row>
-    <row r="183" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B183" s="9"/>
       <c r="C183" s="9"/>
       <c r="D183" s="4"/>
     </row>
-    <row r="184" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D184" s="4"/>
     </row>
-    <row r="185" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B185" s="9"/>
       <c r="C185" s="9"/>
       <c r="D185" s="4"/>
     </row>
-    <row r="186" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D186" s="4"/>
     </row>
-    <row r="187" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B187" s="9"/>
       <c r="C187" s="9"/>
       <c r="D187" s="4"/>
     </row>
-    <row r="188" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D188" s="4"/>
     </row>
-    <row r="189" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B189" s="9"/>
       <c r="C189" s="9"/>
       <c r="D189" s="4"/>
     </row>
-    <row r="190" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D190" s="4"/>
     </row>
-    <row r="191" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B191" s="9"/>
       <c r="C191" s="9"/>
       <c r="D191" s="4"/>
     </row>
-    <row r="192" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D192" s="4"/>
     </row>
-    <row r="193" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B193" s="9"/>
       <c r="C193" s="9"/>
       <c r="D193" s="4"/>
     </row>
-    <row r="194" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D194" s="4"/>
     </row>
-    <row r="195" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B195" s="9"/>
       <c r="C195" s="9"/>
       <c r="D195" s="4"/>
     </row>
-    <row r="196" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D196" s="4"/>
     </row>
-    <row r="197" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B197" s="9"/>
       <c r="C197" s="9"/>
       <c r="D197" s="4"/>
     </row>
-    <row r="198" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D198" s="4"/>
     </row>
-    <row r="199" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B199" s="9"/>
       <c r="C199" s="9"/>
       <c r="D199" s="4"/>
     </row>
-    <row r="200" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D200" s="4"/>
     </row>
-    <row r="201" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B201" s="9"/>
       <c r="C201" s="9"/>
       <c r="D201" s="4"/>
     </row>
-    <row r="202" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D202" s="4"/>
     </row>
-    <row r="203" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B203" s="9"/>
       <c r="C203" s="9"/>
       <c r="D203" s="4"/>
     </row>
-    <row r="204" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D204" s="4"/>
     </row>
-    <row r="205" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B205" s="9"/>
       <c r="C205" s="9"/>
       <c r="D205" s="4"/>
     </row>
-    <row r="206" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D206" s="4"/>
     </row>
-    <row r="207" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B207" s="9"/>
       <c r="C207" s="9"/>
       <c r="D207" s="4"/>
     </row>
-    <row r="208" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D208" s="4"/>
     </row>
-    <row r="209" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B209" s="9"/>
       <c r="C209" s="9"/>
       <c r="D209" s="4"/>
     </row>
-    <row r="210" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D210" s="4"/>
     </row>
-    <row r="211" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B211" s="9"/>
       <c r="C211" s="9"/>
       <c r="D211" s="4"/>
     </row>
-    <row r="212" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D212" s="4"/>
     </row>
-    <row r="213" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B213" s="9"/>
       <c r="C213" s="9"/>
       <c r="D213" s="4"/>
     </row>
-    <row r="214" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D214" s="4"/>
     </row>
-    <row r="215" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B215" s="9"/>
       <c r="C215" s="9"/>
       <c r="D215" s="4"/>
     </row>
-    <row r="216" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D216" s="4"/>
     </row>
-    <row r="217" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B217" s="9"/>
       <c r="C217" s="9"/>
       <c r="D217" s="4"/>
     </row>
-    <row r="218" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D218" s="4"/>
     </row>
-    <row r="219" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B219" s="9"/>
       <c r="C219" s="9"/>
       <c r="D219" s="4"/>
     </row>
-    <row r="220" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D220" s="4"/>
     </row>
-    <row r="221" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B221" s="9"/>
       <c r="C221" s="9"/>
       <c r="D221" s="4"/>
     </row>
-    <row r="222" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D222" s="4"/>
     </row>
-    <row r="223" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B223" s="9"/>
       <c r="C223" s="9"/>
       <c r="D223" s="4"/>
     </row>
-    <row r="224" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D224" s="4"/>
     </row>
-    <row r="225" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B225" s="9"/>
       <c r="C225" s="9"/>
       <c r="D225" s="4"/>
     </row>
-    <row r="226" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D226" s="4"/>
     </row>
-    <row r="227" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B227" s="9"/>
       <c r="C227" s="9"/>
       <c r="D227" s="4"/>
     </row>
-    <row r="228" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D228" s="4"/>
     </row>
-    <row r="229" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B229" s="9"/>
       <c r="C229" s="9"/>
       <c r="D229" s="4"/>
     </row>
-    <row r="230" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D230" s="4"/>
     </row>
-    <row r="231" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B231" s="9"/>
       <c r="C231" s="9"/>
       <c r="D231" s="4"/>
     </row>
-    <row r="232" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D232" s="4"/>
     </row>
-    <row r="233" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B233" s="9"/>
       <c r="C233" s="9"/>
       <c r="D233" s="4"/>
     </row>
-    <row r="234" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D234" s="4"/>
     </row>
-    <row r="235" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B235" s="9"/>
       <c r="C235" s="9"/>
       <c r="D235" s="4"/>
     </row>
-    <row r="236" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D236" s="4"/>
     </row>
-    <row r="237" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B237" s="9"/>
       <c r="C237" s="9"/>
       <c r="D237" s="4"/>
     </row>
-    <row r="238" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D238" s="4"/>
     </row>
-    <row r="239" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B239" s="9"/>
       <c r="C239" s="9"/>
       <c r="D239" s="4"/>
     </row>
-    <row r="240" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D240" s="4"/>
     </row>
-    <row r="241" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B241" s="9"/>
       <c r="C241" s="9"/>
       <c r="D241" s="4"/>
     </row>
-    <row r="242" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D242" s="4"/>
     </row>
-    <row r="243" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B243" s="9"/>
       <c r="C243" s="9"/>
       <c r="D243" s="4"/>
     </row>
-    <row r="244" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D244" s="4"/>
     </row>
-    <row r="245" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B245" s="9"/>
       <c r="C245" s="9"/>
       <c r="D245" s="4"/>
     </row>
-    <row r="246" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D246" s="4"/>
     </row>
-    <row r="247" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B247" s="9"/>
       <c r="C247" s="9"/>
       <c r="D247" s="4"/>
     </row>
-    <row r="248" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D248" s="4"/>
     </row>
-    <row r="249" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B249" s="9"/>
       <c r="C249" s="9"/>
       <c r="D249" s="4"/>
     </row>
-    <row r="250" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D250" s="4"/>
     </row>
-    <row r="251" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B251" s="9"/>
       <c r="C251" s="9"/>
       <c r="D251" s="4"/>
     </row>
-    <row r="252" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D252" s="4"/>
     </row>
-    <row r="253" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B253" s="9"/>
       <c r="C253" s="9"/>
       <c r="D253" s="4"/>
     </row>
-    <row r="254" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D254" s="4"/>
     </row>
-    <row r="255" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B255" s="9"/>
       <c r="C255" s="9"/>
       <c r="D255" s="4"/>
     </row>
-    <row r="256" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D256" s="4"/>
     </row>
-    <row r="257" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B257" s="9"/>
       <c r="C257" s="9"/>
       <c r="D257" s="4"/>
     </row>
-    <row r="258" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D258" s="4"/>
     </row>
-    <row r="259" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B259" s="9"/>
       <c r="C259" s="9"/>
       <c r="D259" s="4"/>
     </row>
-    <row r="260" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D260" s="4"/>
     </row>
-    <row r="261" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B261" s="9"/>
       <c r="C261" s="9"/>
       <c r="D261" s="4"/>
     </row>
-    <row r="262" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D262" s="4"/>
     </row>
-    <row r="263" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B263" s="9"/>
       <c r="C263" s="9"/>
       <c r="D263" s="4"/>
     </row>
-    <row r="264" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D264" s="4"/>
     </row>
-    <row r="265" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B265" s="9"/>
       <c r="C265" s="9"/>
       <c r="D265" s="4"/>
     </row>
-    <row r="266" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D266" s="4"/>
     </row>
-    <row r="267" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B267" s="9"/>
       <c r="C267" s="9"/>
       <c r="D267" s="4"/>
     </row>
-    <row r="268" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D268" s="4"/>
     </row>
-    <row r="269" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B269" s="9"/>
       <c r="C269" s="9"/>
       <c r="D269" s="4"/>
     </row>
-    <row r="270" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D270" s="4"/>
     </row>
-    <row r="271" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B271" s="9"/>
       <c r="C271" s="9"/>
       <c r="D271" s="4"/>
     </row>
-    <row r="272" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D272" s="4"/>
     </row>
-    <row r="273" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B273" s="9"/>
       <c r="C273" s="9"/>
       <c r="D273" s="4"/>
     </row>
-    <row r="274" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D274" s="4"/>
     </row>
-    <row r="275" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B275" s="9"/>
       <c r="C275" s="9"/>
       <c r="D275" s="4"/>
     </row>
-    <row r="276" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D276" s="4"/>
     </row>
-    <row r="277" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B277" s="9"/>
       <c r="C277" s="9"/>
       <c r="D277" s="4"/>
     </row>
-    <row r="278" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D278" s="4"/>
     </row>
-    <row r="279" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B279" s="9"/>
       <c r="C279" s="9"/>
       <c r="D279" s="4"/>
     </row>
-    <row r="280" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D280" s="4"/>
     </row>
-    <row r="281" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B281" s="9"/>
       <c r="C281" s="9"/>
       <c r="D281" s="4"/>
     </row>
-    <row r="282" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D282" s="4"/>
     </row>
-    <row r="283" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B283" s="9"/>
       <c r="C283" s="9"/>
       <c r="D283" s="4"/>
     </row>
-    <row r="284" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D284" s="4"/>
     </row>
-    <row r="285" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B285" s="9"/>
       <c r="C285" s="9"/>
       <c r="D285" s="4"/>
     </row>
-    <row r="286" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D286" s="4"/>
     </row>
-    <row r="287" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B287" s="9"/>
       <c r="C287" s="9"/>
       <c r="D287" s="4"/>
     </row>
-    <row r="288" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D288" s="4"/>
     </row>
-    <row r="289" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B289" s="9"/>
       <c r="C289" s="9"/>
       <c r="D289" s="4"/>
     </row>
-    <row r="290" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D290" s="4"/>
     </row>
-    <row r="291" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B291" s="9"/>
       <c r="C291" s="9"/>
       <c r="D291" s="4"/>
     </row>
-    <row r="292" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D292" s="4"/>
     </row>
-    <row r="293" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B293" s="9"/>
       <c r="C293" s="9"/>
       <c r="D293" s="4"/>
     </row>
-    <row r="294" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D294" s="4"/>
     </row>
-    <row r="295" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B295" s="9"/>
       <c r="C295" s="9"/>
       <c r="D295" s="4"/>
     </row>
-    <row r="296" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D296" s="4"/>
     </row>
-    <row r="297" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B297" s="9"/>
       <c r="C297" s="9"/>
       <c r="D297" s="4"/>
     </row>
-    <row r="298" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D298" s="4"/>
     </row>
-    <row r="299" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B299" s="9"/>
       <c r="C299" s="9"/>
       <c r="D299" s="4"/>
     </row>
-    <row r="300" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D300" s="4"/>
     </row>
-    <row r="301" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B301" s="9"/>
       <c r="C301" s="9"/>
       <c r="D301" s="4"/>
     </row>
-    <row r="302" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D302" s="4"/>
     </row>
-    <row r="303" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B303" s="9"/>
       <c r="C303" s="9"/>
       <c r="D303" s="4"/>
     </row>
-    <row r="304" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D304" s="4"/>
     </row>
-    <row r="305" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B305" s="9"/>
       <c r="C305" s="9"/>
       <c r="D305" s="4"/>
     </row>
-    <row r="306" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D306" s="4"/>
     </row>
-    <row r="307" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B307" s="9"/>
       <c r="C307" s="9"/>
       <c r="D307" s="4"/>
     </row>
-    <row r="308" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D308" s="4"/>
     </row>
-    <row r="309" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B309" s="9"/>
       <c r="C309" s="9"/>
       <c r="D309" s="4"/>
     </row>
-    <row r="310" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D310" s="4"/>
     </row>
-    <row r="311" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B311" s="9"/>
       <c r="C311" s="9"/>
       <c r="D311" s="4"/>
     </row>
-    <row r="312" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D312" s="4"/>
     </row>
-    <row r="313" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B313" s="9"/>
       <c r="C313" s="9"/>
       <c r="D313" s="4"/>
     </row>
-    <row r="314" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D314" s="4"/>
     </row>
-    <row r="315" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B315" s="9"/>
       <c r="C315" s="9"/>
       <c r="D315" s="4"/>
     </row>
-    <row r="316" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D316" s="4"/>
     </row>
-    <row r="317" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B317" s="9"/>
       <c r="C317" s="9"/>
       <c r="D317" s="4"/>
     </row>
-    <row r="318" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D318" s="4"/>
     </row>
-    <row r="319" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B319" s="9"/>
       <c r="C319" s="9"/>
       <c r="D319" s="4"/>
     </row>
-    <row r="320" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D320" s="4"/>
     </row>
-    <row r="321" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B321" s="9"/>
       <c r="C321" s="9"/>
       <c r="D321" s="4"/>
     </row>
-    <row r="322" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="322" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D322" s="4"/>
     </row>
-    <row r="323" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="323" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B323" s="9"/>
       <c r="C323" s="9"/>
       <c r="D323" s="4"/>
     </row>
-    <row r="324" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="324" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D324" s="4"/>
     </row>
-    <row r="325" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B325" s="9"/>
       <c r="C325" s="9"/>
       <c r="D325" s="4"/>
     </row>
-    <row r="326" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="326" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D326" s="4"/>
     </row>
-    <row r="327" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="327" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B327" s="9"/>
       <c r="C327" s="9"/>
       <c r="D327" s="4"/>
     </row>
-    <row r="328" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="328" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D328" s="4"/>
     </row>
-    <row r="329" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="329" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B329" s="9"/>
       <c r="C329" s="9"/>
       <c r="D329" s="4"/>
     </row>
-    <row r="330" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="330" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D330" s="4"/>
     </row>
-    <row r="331" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="331" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B331" s="9"/>
       <c r="C331" s="9"/>
       <c r="D331" s="4"/>
     </row>
-    <row r="332" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="332" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D332" s="4"/>
     </row>
-    <row r="333" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="333" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B333" s="9"/>
       <c r="C333" s="9"/>
       <c r="D333" s="4"/>
     </row>
-    <row r="334" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="334" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D334" s="4"/>
     </row>
-    <row r="335" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="335" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B335" s="9"/>
       <c r="C335" s="9"/>
       <c r="D335" s="4"/>
     </row>
-    <row r="336" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D336" s="4"/>
     </row>
-    <row r="337" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="337" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B337" s="9"/>
       <c r="C337" s="9"/>
       <c r="D337" s="4"/>
     </row>
-    <row r="338" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D338" s="4"/>
     </row>
-    <row r="339" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="339" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B339" s="9"/>
       <c r="C339" s="9"/>
       <c r="D339" s="4"/>
     </row>
-    <row r="340" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="340" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D340" s="4"/>
     </row>
-    <row r="341" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="341" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B341" s="9"/>
       <c r="C341" s="9"/>
       <c r="D341" s="4"/>
     </row>
-    <row r="342" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="342" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D342" s="4"/>
     </row>
-    <row r="343" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="343" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B343" s="9"/>
       <c r="C343" s="9"/>
       <c r="D343" s="4"/>
     </row>
-    <row r="344" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="344" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D344" s="4"/>
     </row>
-    <row r="345" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B345" s="9"/>
       <c r="C345" s="9"/>
       <c r="D345" s="4"/>
     </row>
-    <row r="346" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="346" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D346" s="4"/>
     </row>
-    <row r="347" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B347" s="9"/>
       <c r="C347" s="9"/>
       <c r="D347" s="4"/>
     </row>
-    <row r="348" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="348" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D348" s="4"/>
     </row>
-    <row r="349" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B349" s="9"/>
       <c r="C349" s="9"/>
       <c r="D349" s="4"/>
     </row>
-    <row r="350" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D350" s="4"/>
     </row>
-    <row r="351" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="351" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B351" s="9"/>
       <c r="C351" s="9"/>
       <c r="D351" s="4"/>
     </row>
-    <row r="352" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D352" s="4"/>
     </row>
-    <row r="353" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="353" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B353" s="9"/>
       <c r="C353" s="9"/>
       <c r="D353" s="4"/>
     </row>
-    <row r="354" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D354" s="4"/>
     </row>
-    <row r="355" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B355" s="9"/>
       <c r="C355" s="9"/>
       <c r="D355" s="4"/>
     </row>
-    <row r="356" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D356" s="4"/>
     </row>
-    <row r="357" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="357" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B357" s="9"/>
       <c r="C357" s="9"/>
       <c r="D357" s="4"/>
     </row>
-    <row r="358" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="358" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D358" s="4"/>
     </row>
-    <row r="359" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="359" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B359" s="9"/>
       <c r="C359" s="9"/>
       <c r="D359" s="4"/>
     </row>
-    <row r="360" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="360" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D360" s="4"/>
     </row>
-    <row r="361" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="361" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B361" s="9"/>
       <c r="C361" s="9"/>
       <c r="D361" s="4"/>
     </row>
-    <row r="362" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="362" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D362" s="4"/>
     </row>
-    <row r="363" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="363" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B363" s="9"/>
       <c r="C363" s="9"/>
       <c r="D363" s="4"/>
     </row>
-    <row r="364" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="364" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D364" s="4"/>
     </row>
-    <row r="365" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="365" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B365" s="9"/>
       <c r="C365" s="9"/>
       <c r="D365" s="4"/>
     </row>
-    <row r="366" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="366" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D366" s="4"/>
     </row>
-    <row r="367" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="367" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B367" s="9"/>
       <c r="C367" s="9"/>
       <c r="D367" s="4"/>
     </row>
-    <row r="368" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="368" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D368" s="4"/>
     </row>
-    <row r="369" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="369" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B369" s="9"/>
       <c r="C369" s="9"/>
       <c r="D369" s="4"/>
     </row>
-    <row r="370" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="370" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D370" s="4"/>
     </row>
-    <row r="371" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="371" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B371" s="9"/>
       <c r="C371" s="9"/>
       <c r="D371" s="4"/>
     </row>
-    <row r="372" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D372" s="4"/>
     </row>
-    <row r="373" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="373" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B373" s="9"/>
       <c r="C373" s="9"/>
       <c r="D373" s="4"/>
     </row>
-    <row r="374" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="374" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D374" s="4"/>
     </row>
-    <row r="375" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="375" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B375" s="9"/>
       <c r="C375" s="9"/>
       <c r="D375" s="4"/>
     </row>
-    <row r="376" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="376" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D376" s="4"/>
     </row>
-    <row r="377" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="377" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B377" s="9"/>
       <c r="C377" s="9"/>
       <c r="D377" s="4"/>
     </row>
-    <row r="378" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="378" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D378" s="4"/>
     </row>
-    <row r="379" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="379" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B379" s="9"/>
       <c r="C379" s="9"/>
       <c r="D379" s="4"/>
     </row>
-    <row r="380" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="380" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D380" s="4"/>
     </row>
-    <row r="381" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="381" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B381" s="9"/>
       <c r="C381" s="9"/>
       <c r="D381" s="4"/>
     </row>
-    <row r="382" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D382" s="4"/>
     </row>
-    <row r="383" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="383" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B383" s="9"/>
       <c r="C383" s="9"/>
       <c r="D383" s="4"/>
     </row>
-    <row r="384" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="384" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D384" s="4"/>
     </row>
-    <row r="385" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="385" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B385" s="9"/>
       <c r="C385" s="9"/>
       <c r="D385" s="4"/>
     </row>
-    <row r="386" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="386" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D386" s="4"/>
     </row>
-    <row r="387" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="387" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B387" s="9"/>
       <c r="C387" s="9"/>
       <c r="D387" s="4"/>
     </row>
-    <row r="388" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="388" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D388" s="4"/>
     </row>
-    <row r="389" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="389" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B389" s="9"/>
       <c r="C389" s="9"/>
       <c r="D389" s="4"/>
     </row>
-    <row r="390" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="390" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D390" s="4"/>
     </row>
-    <row r="391" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="391" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B391" s="9"/>
       <c r="C391" s="9"/>
       <c r="D391" s="4"/>
     </row>
-    <row r="392" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="392" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D392" s="4"/>
     </row>
-    <row r="393" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="393" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B393" s="9"/>
       <c r="C393" s="9"/>
       <c r="D393" s="4"/>
     </row>
-    <row r="394" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="394" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D394" s="4"/>
     </row>
-    <row r="395" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="395" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B395" s="9"/>
       <c r="C395" s="9"/>
       <c r="D395" s="4"/>
     </row>
-    <row r="396" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="396" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D396" s="4"/>
     </row>
-    <row r="397" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="397" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B397" s="9"/>
       <c r="C397" s="9"/>
       <c r="D397" s="4"/>
     </row>
-    <row r="398" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="398" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D398" s="4"/>
     </row>
-    <row r="399" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="399" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B399" s="9"/>
       <c r="C399" s="9"/>
       <c r="D399" s="4"/>
     </row>
-    <row r="400" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="400" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D400" s="4"/>
     </row>
-    <row r="401" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="401" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B401" s="9"/>
       <c r="C401" s="9"/>
       <c r="D401" s="4"/>
     </row>
-    <row r="402" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="402" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D402" s="4"/>
     </row>
-    <row r="403" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="403" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B403" s="9"/>
       <c r="C403" s="9"/>
       <c r="D403" s="4"/>
     </row>
-    <row r="404" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="404" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D404" s="4"/>
     </row>
-    <row r="405" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="405" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B405" s="9"/>
       <c r="C405" s="9"/>
       <c r="D405" s="4"/>
     </row>
-    <row r="406" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="406" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D406" s="4"/>
     </row>
-    <row r="407" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="407" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B407" s="9"/>
       <c r="C407" s="9"/>
       <c r="D407" s="4"/>
     </row>
-    <row r="408" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="408" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D408" s="4"/>
     </row>
-    <row r="409" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="409" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B409" s="9"/>
       <c r="C409" s="9"/>
       <c r="D409" s="4"/>
     </row>
-    <row r="410" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="410" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D410" s="4"/>
     </row>
-    <row r="411" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="411" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B411" s="9"/>
       <c r="C411" s="9"/>
       <c r="D411" s="4"/>
     </row>
-    <row r="412" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="412" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D412" s="4"/>
     </row>
-    <row r="413" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="413" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B413" s="9"/>
       <c r="C413" s="9"/>
       <c r="D413" s="4"/>
     </row>
-    <row r="414" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="414" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D414" s="4"/>
     </row>
-    <row r="415" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="415" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B415" s="9"/>
       <c r="C415" s="9"/>
       <c r="D415" s="4"/>
     </row>
-    <row r="416" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="416" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D416" s="4"/>
     </row>
-    <row r="417" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="417" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B417" s="9"/>
       <c r="C417" s="9"/>
       <c r="D417" s="4"/>
     </row>
-    <row r="418" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="418" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D418" s="4"/>
     </row>
-    <row r="419" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="419" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B419" s="9"/>
       <c r="C419" s="9"/>
       <c r="D419" s="4"/>
     </row>
-    <row r="420" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="420" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D420" s="4"/>
     </row>
-    <row r="421" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="421" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B421" s="9"/>
       <c r="C421" s="9"/>
       <c r="D421" s="4"/>
     </row>
-    <row r="422" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="422" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D422" s="4"/>
     </row>
-    <row r="423" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="423" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B423" s="9"/>
       <c r="C423" s="9"/>
       <c r="D423" s="4"/>
     </row>
-    <row r="424" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="424" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D424" s="4"/>
     </row>
-    <row r="425" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="425" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B425" s="9"/>
       <c r="C425" s="9"/>
       <c r="D425" s="4"/>
     </row>
-    <row r="426" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="426" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D426" s="4"/>
     </row>
-    <row r="427" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="427" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B427" s="9"/>
       <c r="C427" s="9"/>
       <c r="D427" s="4"/>
     </row>
-    <row r="428" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="428" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D428" s="4"/>
     </row>
-    <row r="429" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="429" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B429" s="9"/>
       <c r="C429" s="9"/>
       <c r="D429" s="4"/>
     </row>
-    <row r="430" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="430" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D430" s="4"/>
     </row>
-    <row r="431" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="431" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B431" s="9"/>
       <c r="C431" s="9"/>
       <c r="D431" s="4"/>
     </row>
-    <row r="432" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="432" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D432" s="4"/>
     </row>
-    <row r="433" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="433" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B433" s="9"/>
       <c r="C433" s="9"/>
       <c r="D433" s="4"/>
     </row>
-    <row r="434" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="434" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D434" s="4"/>
     </row>
-    <row r="435" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="435" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B435" s="9"/>
       <c r="C435" s="9"/>
       <c r="D435" s="4"/>
     </row>
-    <row r="436" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="436" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D436" s="4"/>
     </row>
-    <row r="437" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="437" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B437" s="9"/>
       <c r="C437" s="9"/>
       <c r="D437" s="4"/>
     </row>
-    <row r="438" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="438" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D438" s="4"/>
     </row>
-    <row r="439" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="439" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B439" s="9"/>
       <c r="C439" s="9"/>
       <c r="D439" s="4"/>
     </row>
-    <row r="440" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="440" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D440" s="4"/>
     </row>
-    <row r="441" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="441" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B441" s="9"/>
       <c r="C441" s="9"/>
       <c r="D441" s="4"/>
     </row>
-    <row r="442" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="442" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D442" s="4"/>
     </row>
-    <row r="443" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="443" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B443" s="9"/>
       <c r="C443" s="9"/>
       <c r="D443" s="4"/>
     </row>
-    <row r="444" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="444" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D444" s="4"/>
     </row>
-    <row r="445" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="445" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B445" s="9"/>
       <c r="C445" s="9"/>
       <c r="D445" s="4"/>
     </row>
-    <row r="446" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="446" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D446" s="4"/>
     </row>
-    <row r="447" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="447" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B447" s="9"/>
       <c r="C447" s="9"/>
       <c r="D447" s="4"/>
     </row>
-    <row r="448" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="448" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D448" s="4"/>
     </row>
-    <row r="449" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="449" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B449" s="9"/>
       <c r="C449" s="9"/>
       <c r="D449" s="4"/>
     </row>
-    <row r="450" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="450" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D450" s="4"/>
     </row>
-    <row r="451" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="451" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B451" s="9"/>
       <c r="C451" s="9"/>
       <c r="D451" s="4"/>
     </row>
-    <row r="452" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="452" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D452" s="4"/>
     </row>
-    <row r="453" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="453" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B453" s="9"/>
       <c r="C453" s="9"/>
       <c r="D453" s="4"/>
     </row>
-    <row r="454" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="454" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D454" s="4"/>
     </row>
-    <row r="455" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="455" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B455" s="9"/>
       <c r="C455" s="9"/>
       <c r="D455" s="4"/>
     </row>
-    <row r="456" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="456" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D456" s="4"/>
     </row>
-    <row r="457" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="457" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B457" s="9"/>
       <c r="C457" s="9"/>
       <c r="D457" s="4"/>
     </row>
-    <row r="458" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="458" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D458" s="4"/>
     </row>
-    <row r="459" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="459" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B459" s="9"/>
       <c r="C459" s="9"/>
       <c r="D459" s="4"/>
     </row>
-    <row r="460" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="460" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D460" s="4"/>
     </row>
-    <row r="461" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="461" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B461" s="9"/>
       <c r="C461" s="9"/>
       <c r="D461" s="4"/>
     </row>
-    <row r="462" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="462" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D462" s="4"/>
     </row>
-    <row r="463" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="463" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B463" s="9"/>
       <c r="C463" s="9"/>
       <c r="D463" s="4"/>
     </row>
-    <row r="464" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="464" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D464" s="4"/>
     </row>
-    <row r="465" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="465" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B465" s="9"/>
       <c r="C465" s="9"/>
       <c r="D465" s="4"/>
     </row>
-    <row r="466" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="466" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D466" s="4"/>
     </row>
-    <row r="467" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="467" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B467" s="9"/>
       <c r="C467" s="9"/>
       <c r="D467" s="4"/>
     </row>
-    <row r="468" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="468" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D468" s="4"/>
     </row>
-    <row r="469" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="469" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B469" s="9"/>
       <c r="C469" s="9"/>
       <c r="D469" s="4"/>
     </row>
-    <row r="470" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="470" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D470" s="4"/>
     </row>
-    <row r="471" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="471" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B471" s="9"/>
       <c r="C471" s="9"/>
       <c r="D471" s="4"/>
     </row>
-    <row r="472" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="472" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D472" s="4"/>
     </row>
-    <row r="473" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="473" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B473" s="9"/>
       <c r="C473" s="9"/>
       <c r="D473" s="4"/>
     </row>
-    <row r="474" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="474" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D474" s="4"/>
     </row>
-    <row r="475" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="475" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B475" s="9"/>
       <c r="C475" s="9"/>
       <c r="D475" s="4"/>
     </row>
-    <row r="476" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="476" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D476" s="4"/>
     </row>
-    <row r="477" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="477" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B477" s="9"/>
       <c r="C477" s="9"/>
       <c r="D477" s="4"/>
     </row>
-    <row r="478" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="478" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D478" s="4"/>
     </row>
-    <row r="479" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="479" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B479" s="9"/>
       <c r="C479" s="9"/>
       <c r="D479" s="4"/>
     </row>
-    <row r="480" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="480" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D480" s="4"/>
     </row>
-    <row r="481" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="481" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B481" s="9"/>
       <c r="C481" s="9"/>
       <c r="D481" s="4"/>
     </row>
-    <row r="482" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="482" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D482" s="4"/>
     </row>
-    <row r="483" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="483" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B483" s="9"/>
       <c r="C483" s="9"/>
       <c r="D483" s="4"/>
     </row>
-    <row r="484" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="484" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D484" s="4"/>
     </row>
-    <row r="485" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="485" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B485" s="9"/>
       <c r="C485" s="9"/>
       <c r="D485" s="4"/>
     </row>
-    <row r="486" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="486" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D486" s="4"/>
     </row>
-    <row r="487" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="487" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B487" s="9"/>
       <c r="C487" s="9"/>
       <c r="D487" s="4"/>
     </row>
-    <row r="488" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="488" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D488" s="4"/>
     </row>
-    <row r="489" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="489" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B489" s="9"/>
       <c r="C489" s="9"/>
       <c r="D489" s="4"/>
     </row>
-    <row r="490" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="490" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D490" s="4"/>
     </row>
-    <row r="491" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="491" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B491" s="9"/>
       <c r="C491" s="9"/>
       <c r="D491" s="4"/>
     </row>
-    <row r="492" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="492" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D492" s="4"/>
     </row>
-    <row r="493" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="493" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B493" s="9"/>
       <c r="C493" s="9"/>
       <c r="D493" s="4"/>
     </row>
-    <row r="494" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="494" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D494" s="4"/>
     </row>
-    <row r="495" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="495" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B495" s="9"/>
       <c r="C495" s="9"/>
       <c r="D495" s="4"/>
     </row>
-    <row r="496" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="496" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D496" s="4"/>
     </row>
-    <row r="497" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="497" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B497" s="9"/>
       <c r="C497" s="9"/>
       <c r="D497" s="4"/>
     </row>
-    <row r="498" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="498" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D498" s="4"/>
     </row>
-    <row r="499" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="499" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B499" s="9"/>
       <c r="C499" s="9"/>
       <c r="D499" s="4"/>
     </row>
-    <row r="500" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="500" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D500" s="4"/>
     </row>
-    <row r="501" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="501" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B501" s="9"/>
       <c r="C501" s="9"/>
       <c r="D501" s="4"/>
     </row>
-    <row r="502" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="502" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D502" s="4"/>
     </row>
-    <row r="503" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="503" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B503" s="9"/>
       <c r="C503" s="9"/>
       <c r="D503" s="4"/>
     </row>
-    <row r="504" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="504" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D504" s="4"/>
     </row>
-    <row r="505" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="505" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B505" s="9"/>
       <c r="C505" s="9"/>
       <c r="D505" s="4"/>
     </row>
-    <row r="506" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="506" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D506" s="4"/>
     </row>
-    <row r="507" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="507" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B507" s="9"/>
       <c r="C507" s="9"/>
       <c r="D507" s="4"/>
     </row>
-    <row r="508" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="508" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D508" s="4"/>
     </row>
-    <row r="509" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="509" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B509" s="9"/>
       <c r="C509" s="9"/>
       <c r="D509" s="4"/>
     </row>
-    <row r="510" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="510" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D510" s="4"/>
     </row>
-    <row r="511" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="511" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B511" s="9"/>
       <c r="C511" s="9"/>
       <c r="D511" s="4"/>
     </row>
-    <row r="512" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="512" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D512" s="4"/>
     </row>
-    <row r="513" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="513" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B513" s="9"/>
       <c r="C513" s="9"/>
       <c r="D513" s="4"/>
     </row>
-    <row r="514" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="514" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D514" s="4"/>
     </row>
-    <row r="515" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="515" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B515" s="9"/>
       <c r="C515" s="9"/>
       <c r="D515" s="4"/>
     </row>
-    <row r="516" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="516" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D516" s="4"/>
     </row>
-    <row r="517" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="517" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B517" s="9"/>
       <c r="C517" s="9"/>
       <c r="D517" s="4"/>
     </row>
-    <row r="518" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="518" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D518" s="4"/>
     </row>
-    <row r="519" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="519" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B519" s="9"/>
       <c r="C519" s="9"/>
       <c r="D519" s="4"/>
     </row>
-    <row r="520" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="520" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D520" s="4"/>
     </row>
-    <row r="521" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="521" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B521" s="9"/>
       <c r="C521" s="9"/>
       <c r="D521" s="4"/>
     </row>
-    <row r="522" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="522" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D522" s="4"/>
     </row>
-    <row r="523" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="523" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B523" s="9"/>
       <c r="C523" s="9"/>
       <c r="D523" s="4"/>
     </row>
-    <row r="524" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="524" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D524" s="4"/>
     </row>
-    <row r="525" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="525" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B525" s="9"/>
       <c r="C525" s="9"/>
       <c r="D525" s="4"/>
     </row>
-    <row r="526" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="526" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D526" s="4"/>
     </row>
-    <row r="527" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="527" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B527" s="9"/>
       <c r="C527" s="9"/>
       <c r="D527" s="4"/>
     </row>
-    <row r="528" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="528" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D528" s="4"/>
     </row>
-    <row r="529" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="529" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B529" s="9"/>
       <c r="C529" s="9"/>
       <c r="D529" s="4"/>
     </row>
-    <row r="530" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="530" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D530" s="4"/>
     </row>
-    <row r="531" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="531" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B531" s="9"/>
       <c r="C531" s="9"/>
       <c r="D531" s="4"/>
     </row>
-    <row r="532" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="532" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D532" s="4"/>
     </row>
-    <row r="533" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="533" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B533" s="9"/>
       <c r="C533" s="9"/>
       <c r="D533" s="4"/>
     </row>
-    <row r="534" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="534" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D534" s="4"/>
     </row>
-    <row r="535" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="535" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B535" s="9"/>
       <c r="C535" s="9"/>
       <c r="D535" s="4"/>
     </row>
-    <row r="536" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="536" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D536" s="4"/>
     </row>
-    <row r="537" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="537" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B537" s="9"/>
       <c r="C537" s="9"/>
       <c r="D537" s="4"/>
     </row>
-    <row r="538" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="538" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D538" s="4"/>
     </row>
-    <row r="539" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="539" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B539" s="9"/>
       <c r="C539" s="9"/>
       <c r="D539" s="4"/>
     </row>
-    <row r="540" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="540" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D540" s="4"/>
     </row>
-    <row r="541" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="541" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B541" s="9"/>
       <c r="C541" s="9"/>
       <c r="D541" s="4"/>
     </row>
-    <row r="542" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="542" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D542" s="4"/>
     </row>
-    <row r="543" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="543" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B543" s="9"/>
       <c r="C543" s="9"/>
       <c r="D543" s="4"/>
     </row>
-    <row r="544" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="544" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D544" s="4"/>
     </row>
-    <row r="545" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="545" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B545" s="9"/>
       <c r="C545" s="9"/>
       <c r="D545" s="4"/>
     </row>
-    <row r="546" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="546" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D546" s="4"/>
     </row>
-    <row r="547" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="547" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B547" s="9"/>
       <c r="C547" s="9"/>
       <c r="D547" s="4"/>
     </row>
-    <row r="548" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="548" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D548" s="4"/>
     </row>
-    <row r="549" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="549" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B549" s="9"/>
       <c r="C549" s="9"/>
       <c r="D549" s="4"/>
     </row>
-    <row r="550" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="550" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D550" s="4"/>
     </row>
-    <row r="551" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="551" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B551" s="9"/>
       <c r="C551" s="9"/>
       <c r="D551" s="4"/>
     </row>
-    <row r="552" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="552" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D552" s="4"/>
     </row>
-    <row r="553" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="553" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B553" s="9"/>
       <c r="C553" s="9"/>
       <c r="D553" s="4"/>
     </row>
-    <row r="554" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="554" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D554" s="4"/>
     </row>
-    <row r="555" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="555" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B555" s="9"/>
       <c r="C555" s="9"/>
       <c r="D555" s="4"/>
     </row>
-    <row r="556" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="556" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D556" s="4"/>
     </row>
-    <row r="557" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="557" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B557" s="9"/>
       <c r="C557" s="9"/>
       <c r="D557" s="4"/>
     </row>
-    <row r="558" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="558" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D558" s="4"/>
     </row>
-    <row r="559" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="559" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B559" s="9"/>
       <c r="C559" s="9"/>
       <c r="D559" s="4"/>
     </row>
-    <row r="560" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="560" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D560" s="4"/>
     </row>
-    <row r="561" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="561" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B561" s="9"/>
       <c r="C561" s="9"/>
       <c r="D561" s="4"/>
     </row>
-    <row r="562" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="562" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D562" s="4"/>
     </row>
-    <row r="563" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="563" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B563" s="9"/>
       <c r="C563" s="9"/>
       <c r="D563" s="4"/>
     </row>
-    <row r="564" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="564" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D564" s="4"/>
     </row>
-    <row r="565" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="565" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B565" s="9"/>
       <c r="C565" s="9"/>
       <c r="D565" s="4"/>
     </row>
-    <row r="566" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="566" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D566" s="4"/>
     </row>
-    <row r="567" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="567" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B567" s="9"/>
       <c r="C567" s="9"/>
       <c r="D567" s="4"/>
     </row>
-    <row r="568" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="568" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D568" s="4"/>
     </row>
-    <row r="569" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="569" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B569" s="9"/>
       <c r="C569" s="9"/>
       <c r="D569" s="4"/>
     </row>
-    <row r="570" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="570" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D570" s="4"/>
     </row>
-    <row r="571" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="571" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B571" s="9"/>
       <c r="C571" s="9"/>
       <c r="D571" s="4"/>
     </row>
-    <row r="572" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="572" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D572" s="4"/>
     </row>
-    <row r="573" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="573" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B573" s="9"/>
       <c r="C573" s="9"/>
       <c r="D573" s="4"/>
     </row>
-    <row r="574" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="574" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D574" s="4"/>
     </row>
-    <row r="575" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="575" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B575" s="9"/>
       <c r="C575" s="9"/>
       <c r="D575" s="4"/>
     </row>
-    <row r="576" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="576" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D576" s="4"/>
     </row>
-    <row r="577" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="577" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B577" s="9"/>
       <c r="C577" s="9"/>
       <c r="D577" s="4"/>
     </row>
-    <row r="578" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="578" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D578" s="4"/>
     </row>
-    <row r="579" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="579" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B579" s="9"/>
       <c r="C579" s="9"/>
       <c r="D579" s="4"/>
     </row>
-    <row r="580" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="580" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D580" s="4"/>
     </row>
-    <row r="581" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="581" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B581" s="9"/>
       <c r="C581" s="9"/>
       <c r="D581" s="4"/>
     </row>
-    <row r="582" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="582" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D582" s="4"/>
     </row>
-    <row r="583" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="583" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B583" s="9"/>
       <c r="C583" s="9"/>
       <c r="D583" s="4"/>
     </row>
-    <row r="584" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="584" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D584" s="4"/>
     </row>
-    <row r="585" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="585" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B585" s="9"/>
       <c r="C585" s="9"/>
       <c r="D585" s="4"/>
     </row>
-    <row r="586" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="586" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D586" s="4"/>
     </row>
-    <row r="587" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="587" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B587" s="9"/>
       <c r="C587" s="9"/>
       <c r="D587" s="4"/>
     </row>
-    <row r="588" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="588" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D588" s="4"/>
     </row>
-    <row r="589" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="589" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B589" s="9"/>
       <c r="C589" s="9"/>
       <c r="D589" s="4"/>
     </row>
-    <row r="590" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="590" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D590" s="4"/>
     </row>
-    <row r="591" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="591" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B591" s="9"/>
       <c r="C591" s="9"/>
       <c r="D591" s="4"/>
     </row>
-    <row r="592" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="592" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D592" s="4"/>
     </row>
-    <row r="593" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="593" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B593" s="9"/>
       <c r="C593" s="9"/>
       <c r="D593" s="4"/>
     </row>
-    <row r="594" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="594" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D594" s="4"/>
     </row>
-    <row r="595" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="595" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B595" s="9"/>
       <c r="C595" s="9"/>
       <c r="D595" s="4"/>
     </row>
-    <row r="596" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="596" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D596" s="4"/>
     </row>
-    <row r="597" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="597" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B597" s="9"/>
       <c r="C597" s="9"/>
       <c r="D597" s="4"/>
     </row>
-    <row r="598" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="598" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D598" s="4"/>
     </row>
-    <row r="599" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="599" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B599" s="9"/>
       <c r="C599" s="9"/>
       <c r="D599" s="4"/>
     </row>
-    <row r="600" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="600" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D600" s="4"/>
     </row>
-    <row r="601" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="601" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B601" s="9"/>
       <c r="C601" s="9"/>
       <c r="D601" s="4"/>
     </row>
-    <row r="602" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="602" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D602" s="4"/>
     </row>
-    <row r="603" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="603" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B603" s="9"/>
       <c r="C603" s="9"/>
       <c r="D603" s="4"/>
     </row>
-    <row r="604" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="604" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D604" s="4"/>
     </row>
-    <row r="605" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="605" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B605" s="9"/>
       <c r="C605" s="9"/>
       <c r="D605" s="4"/>
     </row>
-    <row r="606" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="606" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D606" s="4"/>
     </row>
-    <row r="607" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="607" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B607" s="9"/>
       <c r="C607" s="9"/>
       <c r="D607" s="4"/>
     </row>
-    <row r="608" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="608" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D608" s="4"/>
     </row>
-    <row r="609" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B609" s="9"/>
       <c r="C609" s="9"/>
       <c r="D609" s="4"/>
     </row>
-    <row r="610" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A610" s="7"/>
     </row>
-    <row r="612" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A612" s="7"/>
     </row>
-    <row r="614" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A614" s="7"/>
     </row>
-    <row r="616" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A616" s="7"/>
     </row>
-    <row r="618" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A618" s="7"/>
     </row>
-    <row r="620" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A620" s="7"/>
     </row>
-    <row r="622" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A622" s="7"/>
     </row>
-    <row r="624" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A624" s="7"/>
     </row>
-    <row r="626" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A626" s="7"/>
     </row>
-    <row r="628" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A628" s="7"/>
     </row>
-    <row r="630" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A630" s="7"/>
     </row>
-    <row r="632" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A632" s="7"/>
     </row>
-    <row r="634" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A634" s="7"/>
     </row>
-    <row r="636" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A636" s="7"/>
     </row>
-    <row r="638" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A638" s="7"/>
     </row>
-    <row r="640" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A640" s="7"/>
     </row>
-    <row r="642" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A642" s="7"/>
     </row>
-    <row r="644" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A644" s="7"/>
     </row>
-    <row r="646" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A646" s="7"/>
     </row>
-    <row r="648" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A648" s="7"/>
     </row>
-    <row r="650" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A650" s="7"/>
     </row>
-    <row r="652" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A652" s="7"/>
     </row>
-    <row r="654" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A654" s="7"/>
     </row>
-    <row r="656" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A656" s="7"/>
     </row>
-    <row r="658" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A658" s="7"/>
     </row>
-    <row r="660" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A660" s="7"/>
     </row>
-    <row r="662" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A662" s="7"/>
     </row>
-    <row r="664" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A664" s="7"/>
     </row>
-    <row r="666" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A666" s="7"/>
     </row>
-    <row r="668" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A668" s="7"/>
     </row>
-    <row r="670" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A670" s="7"/>
     </row>
   </sheetData>
@@ -8123,14 +8123,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A58A4A1B-2A66-4BD4-8004-4972898CE4F4}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.453125" customWidth="1"/>
+    <col min="2" max="2" width="18.7265625" customWidth="1"/>
+    <col min="3" max="3" width="16.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>25</v>
       </c>
@@ -8141,7 +8141,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -8149,12 +8149,12 @@
         <v>24</v>
       </c>
       <c r="C2">
-        <v>28.309899999999999</v>
+        <v>28.300899999999999</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -8167,7 +8167,7 @@
       <c r="D3" s="6"/>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -8180,7 +8180,7 @@
       <c r="D4" s="6"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -8193,7 +8193,7 @@
       <c r="D5" s="6"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -8204,7 +8204,7 @@
         <v>43.167899999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -8222,6 +8222,65 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003400CA90578C4C4DACE963633D340941" ma:contentTypeVersion="124" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d6014bca55b54fb6e72613884150ba92">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c32bb4e5-d30f-47c7-b40d-8e40c9a47274" xmlns:ns3="f57c62ac-5b60-40b7-9460-0473ac1a050a" xmlns:ns4="a4282dde-c91e-40c5-9bfe-d2af68f8b118" xmlns:ns5="http://schemas.microsoft.com/sharepoint/v4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9291523fd70371bbc058d49edbaeafd7" ns2:_="" ns3:_="" ns4:_="" ns5:_="">
     <xsd:import namespace="c32bb4e5-d30f-47c7-b40d-8e40c9a47274"/>
@@ -8446,65 +8505,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -8528,7 +8528,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB47F49F-D51B-4FD8-AF9F-70D457A6F3C4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2403B267-BB44-43F1-AB66-61D3B0455A92}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8540,7 +8544,24 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2403B267-BB44-43F1-AB66-61D3B0455A92}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB47F49F-D51B-4FD8-AF9F-70D457A6F3C4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c32bb4e5-d30f-47c7-b40d-8e40c9a47274"/>
+    <ds:schemaRef ds:uri="f57c62ac-5b60-40b7-9460-0473ac1a050a"/>
+    <ds:schemaRef ds:uri="a4282dde-c91e-40c5-9bfe-d2af68f8b118"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8551,6 +8572,8 @@
     <ds:schemaRef ds:uri="c32bb4e5-d30f-47c7-b40d-8e40c9a47274"/>
     <ds:schemaRef ds:uri="9ecf1a6e-3aad-4311-93bc-48574f90e2b0"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v4"/>
+    <ds:schemaRef ds:uri="a4282dde-c91e-40c5-9bfe-d2af68f8b118"/>
+    <ds:schemaRef ds:uri="f57c62ac-5b60-40b7-9460-0473ac1a050a"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>